--- a/semiconductor-wafer-uniformity/inputs/L7734-02_Rs_Measurements.xlsx
+++ b/semiconductor-wafer-uniformity/inputs/L7734-02_Rs_Measurements.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,7 +127,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -602,7 +608,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>84.93000000000001</v>
+        <v>84.93</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>10002</v>
@@ -927,7 +933,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>86.56999999999999</v>
+        <v>86.57</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>10015</v>
@@ -1002,7 +1008,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>86.31999999999999</v>
+        <v>86.32</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>10018</v>
@@ -1027,7 +1033,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>86.34999999999999</v>
+        <v>86.35</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>10019</v>
@@ -1152,7 +1158,7 @@
         <v>58</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>90.06999999999999</v>
+        <v>90.07</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>10024</v>
@@ -1177,7 +1183,7 @@
         <v>58</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>89.84999999999999</v>
+        <v>89.85</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>10025</v>
@@ -1252,7 +1258,7 @@
         <v>58</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>89.18000000000001</v>
+        <v>89.18</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>10028</v>
@@ -1277,7 +1283,7 @@
         <v>58</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>88.68000000000001</v>
+        <v>88.68</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>10029</v>
@@ -1327,7 +1333,7 @@
         <v>58</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>89.99</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>10031</v>
@@ -1393,7 +1399,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>14.24</v>
@@ -1452,7 +1458,7 @@
         <v>73</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>92.18000000000001</v>
+        <v>92.18</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>10036</v>
@@ -1471,7 +1477,7 @@
         <v>14.24</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>73</v>
@@ -1496,7 +1502,7 @@
         <v>-14.24</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E42" s="8" t="n">
         <v>73</v>
@@ -1552,7 +1558,7 @@
         <v>73</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>92.84999999999999</v>
+        <v>92.85</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>10040</v>
@@ -1568,7 +1574,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>14.24</v>
@@ -1593,7 +1599,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>-14.24</v>
@@ -1602,7 +1608,7 @@
         <v>73</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>92.51000000000001</v>
+        <v>92.51</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>10042</v>
@@ -1671,7 +1677,7 @@
         <v>-14.24</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>73</v>
@@ -1696,7 +1702,7 @@
         <v>14.24</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>73</v>
@@ -1768,7 +1774,7 @@
         <v>49</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>-14.24</v>
@@ -2127,7 +2133,7 @@
         <v>40</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>84.76000000000001</v>
+        <v>84.76</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>20014</v>
@@ -2152,7 +2158,7 @@
         <v>40</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>85.81999999999999</v>
+        <v>85.82</v>
       </c>
       <c r="G68" s="8" t="n">
         <v>20015</v>
@@ -2202,7 +2208,7 @@
         <v>40</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>84.79000000000001</v>
+        <v>84.79</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>20017</v>
@@ -2227,7 +2233,7 @@
         <v>40</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>85.20999999999999</v>
+        <v>85.21</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>20018</v>
@@ -2302,7 +2308,7 @@
         <v>40</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>84.45999999999999</v>
+        <v>84.46</v>
       </c>
       <c r="G74" s="8" t="n">
         <v>20021</v>
@@ -2352,7 +2358,7 @@
         <v>58</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>87.73999999999999</v>
+        <v>87.74</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>20023</v>
@@ -2377,7 +2383,7 @@
         <v>58</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>88.09999999999999</v>
+        <v>88.1</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>20024</v>
@@ -2402,7 +2408,7 @@
         <v>58</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>88.34999999999999</v>
+        <v>88.35</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>20025</v>
@@ -2552,7 +2558,7 @@
         <v>58</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>89.18000000000001</v>
+        <v>89.18</v>
       </c>
       <c r="G84" s="8" t="n">
         <v>20031</v>
@@ -2602,7 +2608,7 @@
         <v>58</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>88.81999999999999</v>
+        <v>88.82</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>20033</v>
@@ -2618,7 +2624,7 @@
         <v>34</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>14.24</v>
@@ -2652,7 +2658,7 @@
         <v>73</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>91.95999999999999</v>
+        <v>91.96</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>20035</v>
@@ -2696,13 +2702,13 @@
         <v>14.24</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E90" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>92.06999999999999</v>
+        <v>92.07</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>20037</v>
@@ -2721,13 +2727,13 @@
         <v>-14.24</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>92.29000000000001</v>
+        <v>92.29</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>20038</v>
@@ -2793,7 +2799,7 @@
         <v>41</v>
       </c>
       <c r="C94" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>14.24</v>
@@ -2818,7 +2824,7 @@
         <v>42</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>-14.24</v>
@@ -2827,7 +2833,7 @@
         <v>73</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>91.29000000000001</v>
+        <v>91.29</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>20042</v>
@@ -2896,7 +2902,7 @@
         <v>-14.24</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E98" s="8" t="n">
         <v>73</v>
@@ -2921,13 +2927,13 @@
         <v>14.24</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>91.34999999999999</v>
+        <v>91.35</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>20046</v>
@@ -2993,7 +2999,7 @@
         <v>49</v>
       </c>
       <c r="C102" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>-14.24</v>
@@ -3152,7 +3158,7 @@
         <v>22</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>83.84999999999999</v>
+        <v>83.85</v>
       </c>
       <c r="G108" s="8" t="n">
         <v>30006</v>
@@ -3202,7 +3208,7 @@
         <v>22</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>82.84999999999999</v>
+        <v>82.85</v>
       </c>
       <c r="G110" s="8" t="n">
         <v>30008</v>
@@ -3252,7 +3258,7 @@
         <v>40</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>84.90000000000001</v>
+        <v>84.9</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>30010</v>
@@ -3302,7 +3308,7 @@
         <v>40</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>85.04000000000001</v>
+        <v>85.04</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>30012</v>
@@ -3327,7 +3333,7 @@
         <v>40</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>85.01000000000001</v>
+        <v>85.01</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>30013</v>
@@ -3527,7 +3533,7 @@
         <v>40</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>84.76000000000001</v>
+        <v>84.76</v>
       </c>
       <c r="G123" s="5" t="n">
         <v>30021</v>
@@ -3577,7 +3583,7 @@
         <v>58</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>87.81999999999999</v>
+        <v>87.82</v>
       </c>
       <c r="G125" s="5" t="n">
         <v>30023</v>
@@ -3602,7 +3608,7 @@
         <v>58</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>88.84999999999999</v>
+        <v>88.85</v>
       </c>
       <c r="G126" s="8" t="n">
         <v>30024</v>
@@ -3627,7 +3633,7 @@
         <v>58</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>88.79000000000001</v>
+        <v>88.79</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>30025</v>
@@ -3652,7 +3658,7 @@
         <v>58</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>88.51000000000001</v>
+        <v>88.51</v>
       </c>
       <c r="G128" s="8" t="n">
         <v>30026</v>
@@ -3677,7 +3683,7 @@
         <v>58</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>88.34999999999999</v>
+        <v>88.35</v>
       </c>
       <c r="G129" s="5" t="n">
         <v>30027</v>
@@ -3843,7 +3849,7 @@
         <v>34</v>
       </c>
       <c r="C136" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>14.24</v>
@@ -3921,7 +3927,7 @@
         <v>14.24</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E139" s="5" t="n">
         <v>73</v>
@@ -3946,13 +3952,13 @@
         <v>-14.24</v>
       </c>
       <c r="D140" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E140" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>91.26000000000001</v>
+        <v>91.26</v>
       </c>
       <c r="G140" s="8" t="n">
         <v>30038</v>
@@ -4018,7 +4024,7 @@
         <v>41</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D143" s="5" t="n">
         <v>14.24</v>
@@ -4043,7 +4049,7 @@
         <v>42</v>
       </c>
       <c r="C144" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D144" s="8" t="n">
         <v>-14.24</v>
@@ -4121,7 +4127,7 @@
         <v>-14.24</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>73</v>
@@ -4146,13 +4152,13 @@
         <v>14.24</v>
       </c>
       <c r="D148" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F148" s="9" t="n">
-        <v>91.34999999999999</v>
+        <v>91.35</v>
       </c>
       <c r="G148" s="8" t="n">
         <v>30046</v>
@@ -4218,7 +4224,7 @@
         <v>49</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>-14.24</v>
@@ -4227,7 +4233,7 @@
         <v>73</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>91.34999999999999</v>
+        <v>91.35</v>
       </c>
       <c r="G151" s="5" t="n">
         <v>30049</v>
@@ -4327,7 +4333,7 @@
         <v>22</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>82.15000000000001</v>
+        <v>82.15</v>
       </c>
       <c r="G155" s="5" t="n">
         <v>40003</v>
@@ -4377,7 +4383,7 @@
         <v>22</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>83.01000000000001</v>
+        <v>83.01</v>
       </c>
       <c r="G157" s="5" t="n">
         <v>40005</v>
@@ -4502,7 +4508,7 @@
         <v>40</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>84.23999999999999</v>
+        <v>84.24</v>
       </c>
       <c r="G162" s="8" t="n">
         <v>40010</v>
@@ -4527,7 +4533,7 @@
         <v>40</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>85.29000000000001</v>
+        <v>85.29</v>
       </c>
       <c r="G163" s="5" t="n">
         <v>40011</v>
@@ -4602,7 +4608,7 @@
         <v>40</v>
       </c>
       <c r="F166" s="9" t="n">
-        <v>85.15000000000001</v>
+        <v>85.15</v>
       </c>
       <c r="G166" s="8" t="n">
         <v>40014</v>
@@ -4652,7 +4658,7 @@
         <v>40</v>
       </c>
       <c r="F168" s="9" t="n">
-        <v>85.06999999999999</v>
+        <v>85.07</v>
       </c>
       <c r="G168" s="8" t="n">
         <v>40016</v>
@@ -4677,7 +4683,7 @@
         <v>40</v>
       </c>
       <c r="F169" s="6" t="n">
-        <v>85.34999999999999</v>
+        <v>85.35</v>
       </c>
       <c r="G169" s="5" t="n">
         <v>40017</v>
@@ -4802,7 +4808,7 @@
         <v>58</v>
       </c>
       <c r="F174" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G174" s="8" t="n">
         <v>40022</v>
@@ -4877,7 +4883,7 @@
         <v>58</v>
       </c>
       <c r="F177" s="6" t="n">
-        <v>87.43000000000001</v>
+        <v>87.43</v>
       </c>
       <c r="G177" s="5" t="n">
         <v>40025</v>
@@ -4902,7 +4908,7 @@
         <v>58</v>
       </c>
       <c r="F178" s="9" t="n">
-        <v>87.73999999999999</v>
+        <v>87.74</v>
       </c>
       <c r="G178" s="8" t="n">
         <v>40026</v>
@@ -5093,7 +5099,7 @@
         <v>34</v>
       </c>
       <c r="C186" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D186" s="8" t="n">
         <v>14.24</v>
@@ -5152,7 +5158,7 @@
         <v>73</v>
       </c>
       <c r="F188" s="9" t="n">
-        <v>90.79000000000001</v>
+        <v>90.79</v>
       </c>
       <c r="G188" s="8" t="n">
         <v>40036</v>
@@ -5171,7 +5177,7 @@
         <v>14.24</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E189" s="5" t="n">
         <v>73</v>
@@ -5196,13 +5202,13 @@
         <v>-14.24</v>
       </c>
       <c r="D190" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E190" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F190" s="9" t="n">
-        <v>90.98999999999999</v>
+        <v>90.99</v>
       </c>
       <c r="G190" s="8" t="n">
         <v>40038</v>
@@ -5252,7 +5258,7 @@
         <v>73</v>
       </c>
       <c r="F192" s="9" t="n">
-        <v>90.76000000000001</v>
+        <v>90.76</v>
       </c>
       <c r="G192" s="8" t="n">
         <v>40040</v>
@@ -5268,7 +5274,7 @@
         <v>41</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D193" s="5" t="n">
         <v>14.24</v>
@@ -5277,7 +5283,7 @@
         <v>73</v>
       </c>
       <c r="F193" s="6" t="n">
-        <v>92.20999999999999</v>
+        <v>92.21</v>
       </c>
       <c r="G193" s="5" t="n">
         <v>40041</v>
@@ -5293,7 +5299,7 @@
         <v>42</v>
       </c>
       <c r="C194" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D194" s="8" t="n">
         <v>-14.24</v>
@@ -5302,7 +5308,7 @@
         <v>73</v>
       </c>
       <c r="F194" s="9" t="n">
-        <v>92.23999999999999</v>
+        <v>92.24</v>
       </c>
       <c r="G194" s="8" t="n">
         <v>40042</v>
@@ -5371,7 +5377,7 @@
         <v>-14.24</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E197" s="5" t="n">
         <v>73</v>
@@ -5396,7 +5402,7 @@
         <v>14.24</v>
       </c>
       <c r="D198" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E198" s="8" t="n">
         <v>73</v>
@@ -5468,7 +5474,7 @@
         <v>49</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D201" s="5" t="n">
         <v>-14.24</v>
@@ -5502,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="F202" s="9" t="n">
-        <v>81.56999999999999</v>
+        <v>81.57</v>
       </c>
       <c r="G202" s="8" t="n">
         <v>50001</v>
@@ -5527,7 +5533,7 @@
         <v>22</v>
       </c>
       <c r="F203" s="6" t="n">
-        <v>83.65000000000001</v>
+        <v>83.65</v>
       </c>
       <c r="G203" s="5" t="n">
         <v>50002</v>
@@ -5577,7 +5583,7 @@
         <v>22</v>
       </c>
       <c r="F205" s="6" t="n">
-        <v>82.73999999999999</v>
+        <v>82.74</v>
       </c>
       <c r="G205" s="5" t="n">
         <v>50004</v>
@@ -5827,7 +5833,7 @@
         <v>40</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>85.23999999999999</v>
+        <v>85.24</v>
       </c>
       <c r="G215" s="5" t="n">
         <v>50014</v>
@@ -5902,7 +5908,7 @@
         <v>40</v>
       </c>
       <c r="F218" s="9" t="n">
-        <v>84.56999999999999</v>
+        <v>84.57</v>
       </c>
       <c r="G218" s="8" t="n">
         <v>50017</v>
@@ -5927,7 +5933,7 @@
         <v>40</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>85.70999999999999</v>
+        <v>85.71</v>
       </c>
       <c r="G219" s="5" t="n">
         <v>50018</v>
@@ -5952,7 +5958,7 @@
         <v>40</v>
       </c>
       <c r="F220" s="9" t="n">
-        <v>85.18000000000001</v>
+        <v>85.18</v>
       </c>
       <c r="G220" s="8" t="n">
         <v>50019</v>
@@ -5977,7 +5983,7 @@
         <v>40</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>85.04000000000001</v>
+        <v>85.04</v>
       </c>
       <c r="G221" s="5" t="n">
         <v>50020</v>
@@ -6027,7 +6033,7 @@
         <v>58</v>
       </c>
       <c r="F223" s="6" t="n">
-        <v>88.76000000000001</v>
+        <v>88.76</v>
       </c>
       <c r="G223" s="5" t="n">
         <v>50022</v>
@@ -6052,7 +6058,7 @@
         <v>58</v>
       </c>
       <c r="F224" s="9" t="n">
-        <v>87.93000000000001</v>
+        <v>87.93</v>
       </c>
       <c r="G224" s="8" t="n">
         <v>50023</v>
@@ -6102,7 +6108,7 @@
         <v>58</v>
       </c>
       <c r="F226" s="9" t="n">
-        <v>88.45999999999999</v>
+        <v>88.46</v>
       </c>
       <c r="G226" s="8" t="n">
         <v>50025</v>
@@ -6152,7 +6158,7 @@
         <v>58</v>
       </c>
       <c r="F228" s="9" t="n">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="G228" s="8" t="n">
         <v>50027</v>
@@ -6318,7 +6324,7 @@
         <v>34</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>14.24</v>
@@ -6396,7 +6402,7 @@
         <v>14.24</v>
       </c>
       <c r="D238" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E238" s="8" t="n">
         <v>73</v>
@@ -6421,13 +6427,13 @@
         <v>-14.24</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E239" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F239" s="6" t="n">
-        <v>91.43000000000001</v>
+        <v>91.43</v>
       </c>
       <c r="G239" s="5" t="n">
         <v>50038</v>
@@ -6452,7 +6458,7 @@
         <v>73</v>
       </c>
       <c r="F240" s="9" t="n">
-        <v>91.65000000000001</v>
+        <v>91.65</v>
       </c>
       <c r="G240" s="8" t="n">
         <v>50039</v>
@@ -6493,7 +6499,7 @@
         <v>41</v>
       </c>
       <c r="C242" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D242" s="8" t="n">
         <v>14.24</v>
@@ -6518,7 +6524,7 @@
         <v>42</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>-14.24</v>
@@ -6527,7 +6533,7 @@
         <v>73</v>
       </c>
       <c r="F243" s="6" t="n">
-        <v>92.26000000000001</v>
+        <v>92.26</v>
       </c>
       <c r="G243" s="5" t="n">
         <v>50042</v>
@@ -6596,7 +6602,7 @@
         <v>-14.24</v>
       </c>
       <c r="D246" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E246" s="8" t="n">
         <v>73</v>
@@ -6621,7 +6627,7 @@
         <v>14.24</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E247" s="5" t="n">
         <v>73</v>
@@ -6693,7 +6699,7 @@
         <v>49</v>
       </c>
       <c r="C250" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D250" s="8" t="n">
         <v>-14.24</v>
@@ -6702,7 +6708,7 @@
         <v>73</v>
       </c>
       <c r="F250" s="9" t="n">
-        <v>91.51000000000001</v>
+        <v>91.51</v>
       </c>
       <c r="G250" s="8" t="n">
         <v>50049</v>
@@ -6777,7 +6783,7 @@
         <v>22</v>
       </c>
       <c r="F253" s="6" t="n">
-        <v>82.29000000000001</v>
+        <v>82.29</v>
       </c>
       <c r="G253" s="5" t="n">
         <v>60003</v>
@@ -6852,7 +6858,7 @@
         <v>22</v>
       </c>
       <c r="F256" s="9" t="n">
-        <v>82.31999999999999</v>
+        <v>82.32</v>
       </c>
       <c r="G256" s="8" t="n">
         <v>60006</v>
@@ -6877,7 +6883,7 @@
         <v>22</v>
       </c>
       <c r="F257" s="6" t="n">
-        <v>83.29000000000001</v>
+        <v>83.29</v>
       </c>
       <c r="G257" s="5" t="n">
         <v>60007</v>
@@ -7002,7 +7008,7 @@
         <v>40</v>
       </c>
       <c r="F262" s="9" t="n">
-        <v>84.31999999999999</v>
+        <v>84.32</v>
       </c>
       <c r="G262" s="8" t="n">
         <v>60012</v>
@@ -7077,7 +7083,7 @@
         <v>40</v>
       </c>
       <c r="F265" s="6" t="n">
-        <v>84.40000000000001</v>
+        <v>84.4</v>
       </c>
       <c r="G265" s="5" t="n">
         <v>60015</v>
@@ -7152,7 +7158,7 @@
         <v>40</v>
       </c>
       <c r="F268" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.1</v>
       </c>
       <c r="G268" s="8" t="n">
         <v>60018</v>
@@ -7227,7 +7233,7 @@
         <v>40</v>
       </c>
       <c r="F271" s="6" t="n">
-        <v>83.93000000000001</v>
+        <v>83.93</v>
       </c>
       <c r="G271" s="5" t="n">
         <v>60021</v>
@@ -7277,7 +7283,7 @@
         <v>58</v>
       </c>
       <c r="F273" s="6" t="n">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G273" s="5" t="n">
         <v>60023</v>
@@ -7327,7 +7333,7 @@
         <v>58</v>
       </c>
       <c r="F275" s="6" t="n">
-        <v>87.93000000000001</v>
+        <v>87.93</v>
       </c>
       <c r="G275" s="5" t="n">
         <v>60025</v>
@@ -7352,7 +7358,7 @@
         <v>58</v>
       </c>
       <c r="F276" s="9" t="n">
-        <v>87.56999999999999</v>
+        <v>87.57</v>
       </c>
       <c r="G276" s="8" t="n">
         <v>60026</v>
@@ -7427,7 +7433,7 @@
         <v>58</v>
       </c>
       <c r="F279" s="6" t="n">
-        <v>88.01000000000001</v>
+        <v>88.01</v>
       </c>
       <c r="G279" s="5" t="n">
         <v>60029</v>
@@ -7452,7 +7458,7 @@
         <v>58</v>
       </c>
       <c r="F280" s="9" t="n">
-        <v>87.29000000000001</v>
+        <v>87.29</v>
       </c>
       <c r="G280" s="8" t="n">
         <v>60030</v>
@@ -7477,7 +7483,7 @@
         <v>58</v>
       </c>
       <c r="F281" s="6" t="n">
-        <v>87.68000000000001</v>
+        <v>87.68</v>
       </c>
       <c r="G281" s="5" t="n">
         <v>60031</v>
@@ -7543,7 +7549,7 @@
         <v>34</v>
       </c>
       <c r="C284" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D284" s="8" t="n">
         <v>14.24</v>
@@ -7577,7 +7583,7 @@
         <v>73</v>
       </c>
       <c r="F285" s="6" t="n">
-        <v>91.84999999999999</v>
+        <v>91.85</v>
       </c>
       <c r="G285" s="5" t="n">
         <v>60035</v>
@@ -7621,7 +7627,7 @@
         <v>14.24</v>
       </c>
       <c r="D287" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E287" s="5" t="n">
         <v>73</v>
@@ -7646,7 +7652,7 @@
         <v>-14.24</v>
       </c>
       <c r="D288" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E288" s="8" t="n">
         <v>73</v>
@@ -7718,7 +7724,7 @@
         <v>41</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D291" s="5" t="n">
         <v>14.24</v>
@@ -7743,7 +7749,7 @@
         <v>42</v>
       </c>
       <c r="C292" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D292" s="8" t="n">
         <v>-14.24</v>
@@ -7752,7 +7758,7 @@
         <v>73</v>
       </c>
       <c r="F292" s="9" t="n">
-        <v>90.79000000000001</v>
+        <v>90.79</v>
       </c>
       <c r="G292" s="8" t="n">
         <v>60042</v>
@@ -7821,7 +7827,7 @@
         <v>-14.24</v>
       </c>
       <c r="D295" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E295" s="5" t="n">
         <v>73</v>
@@ -7846,7 +7852,7 @@
         <v>14.24</v>
       </c>
       <c r="D296" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E296" s="8" t="n">
         <v>73</v>
@@ -7877,7 +7883,7 @@
         <v>73</v>
       </c>
       <c r="F297" s="6" t="n">
-        <v>90.70999999999999</v>
+        <v>90.71</v>
       </c>
       <c r="G297" s="5" t="n">
         <v>60047</v>
@@ -7902,7 +7908,7 @@
         <v>73</v>
       </c>
       <c r="F298" s="9" t="n">
-        <v>91.76000000000001</v>
+        <v>91.76</v>
       </c>
       <c r="G298" s="8" t="n">
         <v>60048</v>
@@ -7918,7 +7924,7 @@
         <v>49</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D299" s="5" t="n">
         <v>-14.24</v>
@@ -8002,7 +8008,7 @@
         <v>22</v>
       </c>
       <c r="F302" s="9" t="n">
-        <v>85.09999999999999</v>
+        <v>85.1</v>
       </c>
       <c r="G302" s="8" t="n">
         <v>70003</v>
@@ -8127,7 +8133,7 @@
         <v>22</v>
       </c>
       <c r="F307" s="6" t="n">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G307" s="5" t="n">
         <v>70008</v>
@@ -8177,7 +8183,7 @@
         <v>40</v>
       </c>
       <c r="F309" s="6" t="n">
-        <v>86.51000000000001</v>
+        <v>86.51</v>
       </c>
       <c r="G309" s="5" t="n">
         <v>70010</v>
@@ -8277,7 +8283,7 @@
         <v>40</v>
       </c>
       <c r="F313" s="6" t="n">
-        <v>85.79000000000001</v>
+        <v>85.79</v>
       </c>
       <c r="G313" s="5" t="n">
         <v>70014</v>
@@ -8327,7 +8333,7 @@
         <v>40</v>
       </c>
       <c r="F315" s="6" t="n">
-        <v>86.06999999999999</v>
+        <v>86.07</v>
       </c>
       <c r="G315" s="5" t="n">
         <v>70016</v>
@@ -8352,7 +8358,7 @@
         <v>40</v>
       </c>
       <c r="F316" s="9" t="n">
-        <v>86.23999999999999</v>
+        <v>86.24</v>
       </c>
       <c r="G316" s="8" t="n">
         <v>70017</v>
@@ -8502,7 +8508,7 @@
         <v>58</v>
       </c>
       <c r="F322" s="9" t="n">
-        <v>89.51000000000001</v>
+        <v>89.51</v>
       </c>
       <c r="G322" s="8" t="n">
         <v>70023</v>
@@ -8602,7 +8608,7 @@
         <v>58</v>
       </c>
       <c r="F326" s="9" t="n">
-        <v>90.31999999999999</v>
+        <v>90.32</v>
       </c>
       <c r="G326" s="8" t="n">
         <v>70027</v>
@@ -8627,7 +8633,7 @@
         <v>58</v>
       </c>
       <c r="F327" s="6" t="n">
-        <v>95.40000000000001</v>
+        <v>95.4</v>
       </c>
       <c r="G327" s="5" t="n">
         <v>70028</v>
@@ -8727,7 +8733,7 @@
         <v>58</v>
       </c>
       <c r="F331" s="6" t="n">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G331" s="5" t="n">
         <v>70032</v>
@@ -8752,7 +8758,7 @@
         <v>58</v>
       </c>
       <c r="F332" s="9" t="n">
-        <v>88.76000000000001</v>
+        <v>88.76</v>
       </c>
       <c r="G332" s="8" t="n">
         <v>70033</v>
@@ -8768,7 +8774,7 @@
         <v>34</v>
       </c>
       <c r="C333" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D333" s="5" t="n">
         <v>14.24</v>
@@ -8802,7 +8808,7 @@
         <v>73</v>
       </c>
       <c r="F334" s="9" t="n">
-        <v>93.81999999999999</v>
+        <v>93.82</v>
       </c>
       <c r="G334" s="8" t="n">
         <v>70035</v>
@@ -8846,7 +8852,7 @@
         <v>14.24</v>
       </c>
       <c r="D336" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E336" s="8" t="n">
         <v>73</v>
@@ -8871,7 +8877,7 @@
         <v>-14.24</v>
       </c>
       <c r="D337" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E337" s="5" t="n">
         <v>73</v>
@@ -8902,7 +8908,7 @@
         <v>73</v>
       </c>
       <c r="F338" s="9" t="n">
-        <v>93.04000000000001</v>
+        <v>93.04</v>
       </c>
       <c r="G338" s="8" t="n">
         <v>70039</v>
@@ -8943,7 +8949,7 @@
         <v>41</v>
       </c>
       <c r="C340" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D340" s="8" t="n">
         <v>14.24</v>
@@ -8968,7 +8974,7 @@
         <v>42</v>
       </c>
       <c r="C341" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D341" s="5" t="n">
         <v>-14.24</v>
@@ -9046,13 +9052,13 @@
         <v>-14.24</v>
       </c>
       <c r="D344" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E344" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F344" s="9" t="n">
-        <v>93.70999999999999</v>
+        <v>93.71</v>
       </c>
       <c r="G344" s="8" t="n">
         <v>70045</v>
@@ -9071,13 +9077,13 @@
         <v>14.24</v>
       </c>
       <c r="D345" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E345" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F345" s="6" t="n">
-        <v>92.34999999999999</v>
+        <v>92.35</v>
       </c>
       <c r="G345" s="5" t="n">
         <v>70046</v>
@@ -9143,7 +9149,7 @@
         <v>49</v>
       </c>
       <c r="C348" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D348" s="8" t="n">
         <v>-14.24</v>
@@ -9177,7 +9183,7 @@
         <v>58</v>
       </c>
       <c r="F349" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.9</v>
       </c>
       <c r="G349" s="5" t="n">
         <v>75028</v>
@@ -9227,7 +9233,7 @@
         <v>22</v>
       </c>
       <c r="F351" s="6" t="n">
-        <v>82.93000000000001</v>
+        <v>82.93</v>
       </c>
       <c r="G351" s="5" t="n">
         <v>80002</v>
@@ -9252,7 +9258,7 @@
         <v>22</v>
       </c>
       <c r="F352" s="9" t="n">
-        <v>83.98999999999999</v>
+        <v>83.99</v>
       </c>
       <c r="G352" s="8" t="n">
         <v>80003</v>
@@ -9277,7 +9283,7 @@
         <v>22</v>
       </c>
       <c r="F353" s="6" t="n">
-        <v>83.23999999999999</v>
+        <v>83.24</v>
       </c>
       <c r="G353" s="5" t="n">
         <v>80004</v>
@@ -9302,7 +9308,7 @@
         <v>22</v>
       </c>
       <c r="F354" s="9" t="n">
-        <v>82.51000000000001</v>
+        <v>82.51</v>
       </c>
       <c r="G354" s="8" t="n">
         <v>80005</v>
@@ -9427,7 +9433,7 @@
         <v>40</v>
       </c>
       <c r="F359" s="6" t="n">
-        <v>84.65000000000001</v>
+        <v>84.65</v>
       </c>
       <c r="G359" s="5" t="n">
         <v>80010</v>
@@ -9452,7 +9458,7 @@
         <v>40</v>
       </c>
       <c r="F360" s="9" t="n">
-        <v>84.56999999999999</v>
+        <v>84.57</v>
       </c>
       <c r="G360" s="8" t="n">
         <v>80011</v>
@@ -9477,7 +9483,7 @@
         <v>40</v>
       </c>
       <c r="F361" s="6" t="n">
-        <v>85.06999999999999</v>
+        <v>85.07</v>
       </c>
       <c r="G361" s="5" t="n">
         <v>80012</v>
@@ -9552,7 +9558,7 @@
         <v>40</v>
       </c>
       <c r="F364" s="9" t="n">
-        <v>84.54000000000001</v>
+        <v>84.54</v>
       </c>
       <c r="G364" s="8" t="n">
         <v>80015</v>
@@ -9602,7 +9608,7 @@
         <v>40</v>
       </c>
       <c r="F366" s="9" t="n">
-        <v>85.45999999999999</v>
+        <v>85.46</v>
       </c>
       <c r="G366" s="8" t="n">
         <v>80017</v>
@@ -9627,7 +9633,7 @@
         <v>40</v>
       </c>
       <c r="F367" s="6" t="n">
-        <v>84.48999999999999</v>
+        <v>84.49</v>
       </c>
       <c r="G367" s="5" t="n">
         <v>80018</v>
@@ -9802,7 +9808,7 @@
         <v>58</v>
       </c>
       <c r="F374" s="9" t="n">
-        <v>88.59999999999999</v>
+        <v>88.6</v>
       </c>
       <c r="G374" s="8" t="n">
         <v>80025</v>
@@ -9827,7 +9833,7 @@
         <v>58</v>
       </c>
       <c r="F375" s="6" t="n">
-        <v>88.65000000000001</v>
+        <v>88.65</v>
       </c>
       <c r="G375" s="5" t="n">
         <v>80026</v>
@@ -9852,7 +9858,7 @@
         <v>58</v>
       </c>
       <c r="F376" s="9" t="n">
-        <v>88.54000000000001</v>
+        <v>88.54</v>
       </c>
       <c r="G376" s="8" t="n">
         <v>80027</v>
@@ -9927,7 +9933,7 @@
         <v>58</v>
       </c>
       <c r="F379" s="6" t="n">
-        <v>88.81999999999999</v>
+        <v>88.82</v>
       </c>
       <c r="G379" s="5" t="n">
         <v>80030</v>
@@ -9952,7 +9958,7 @@
         <v>58</v>
       </c>
       <c r="F380" s="9" t="n">
-        <v>88.98999999999999</v>
+        <v>88.99</v>
       </c>
       <c r="G380" s="8" t="n">
         <v>80031</v>
@@ -10002,7 +10008,7 @@
         <v>58</v>
       </c>
       <c r="F382" s="9" t="n">
-        <v>88.06999999999999</v>
+        <v>88.07</v>
       </c>
       <c r="G382" s="8" t="n">
         <v>80033</v>
@@ -10018,7 +10024,7 @@
         <v>34</v>
       </c>
       <c r="C383" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D383" s="5" t="n">
         <v>14.24</v>
@@ -10027,7 +10033,7 @@
         <v>73</v>
       </c>
       <c r="F383" s="6" t="n">
-        <v>91.73999999999999</v>
+        <v>91.74</v>
       </c>
       <c r="G383" s="5" t="n">
         <v>80034</v>
@@ -10052,7 +10058,7 @@
         <v>73</v>
       </c>
       <c r="F384" s="9" t="n">
-        <v>91.84999999999999</v>
+        <v>91.85</v>
       </c>
       <c r="G384" s="8" t="n">
         <v>80035</v>
@@ -10096,7 +10102,7 @@
         <v>14.24</v>
       </c>
       <c r="D386" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E386" s="8" t="n">
         <v>73</v>
@@ -10121,13 +10127,13 @@
         <v>-14.24</v>
       </c>
       <c r="D387" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E387" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F387" s="6" t="n">
-        <v>91.48999999999999</v>
+        <v>91.49</v>
       </c>
       <c r="G387" s="5" t="n">
         <v>80038</v>
@@ -10152,7 +10158,7 @@
         <v>73</v>
       </c>
       <c r="F388" s="9" t="n">
-        <v>92.56999999999999</v>
+        <v>92.57</v>
       </c>
       <c r="G388" s="8" t="n">
         <v>80039</v>
@@ -10193,7 +10199,7 @@
         <v>41</v>
       </c>
       <c r="C390" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D390" s="8" t="n">
         <v>14.24</v>
@@ -10218,7 +10224,7 @@
         <v>42</v>
       </c>
       <c r="C391" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D391" s="5" t="n">
         <v>-14.24</v>
@@ -10296,7 +10302,7 @@
         <v>-14.24</v>
       </c>
       <c r="D394" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E394" s="8" t="n">
         <v>73</v>
@@ -10321,7 +10327,7 @@
         <v>14.24</v>
       </c>
       <c r="D395" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E395" s="5" t="n">
         <v>73</v>
@@ -10377,7 +10383,7 @@
         <v>73</v>
       </c>
       <c r="F397" s="6" t="n">
-        <v>92.26000000000001</v>
+        <v>92.26</v>
       </c>
       <c r="G397" s="5" t="n">
         <v>80048</v>
@@ -10393,7 +10399,7 @@
         <v>49</v>
       </c>
       <c r="C398" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D398" s="8" t="n">
         <v>-14.24</v>
@@ -10402,7 +10408,7 @@
         <v>73</v>
       </c>
       <c r="F398" s="9" t="n">
-        <v>92.26000000000001</v>
+        <v>92.26</v>
       </c>
       <c r="G398" s="8" t="n">
         <v>80049</v>
@@ -10552,7 +10558,7 @@
         <v>22</v>
       </c>
       <c r="F404" s="9" t="n">
-        <v>82.48999999999999</v>
+        <v>82.49</v>
       </c>
       <c r="G404" s="8" t="n">
         <v>90006</v>
@@ -10577,7 +10583,7 @@
         <v>22</v>
       </c>
       <c r="F405" s="6" t="n">
-        <v>82.73999999999999</v>
+        <v>82.74</v>
       </c>
       <c r="G405" s="5" t="n">
         <v>90007</v>
@@ -10627,7 +10633,7 @@
         <v>22</v>
       </c>
       <c r="F407" s="6" t="n">
-        <v>81.98999999999999</v>
+        <v>81.99</v>
       </c>
       <c r="G407" s="5" t="n">
         <v>90009</v>
@@ -10702,7 +10708,7 @@
         <v>40</v>
       </c>
       <c r="F410" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.1</v>
       </c>
       <c r="G410" s="8" t="n">
         <v>90012</v>
@@ -10727,7 +10733,7 @@
         <v>40</v>
       </c>
       <c r="F411" s="6" t="n">
-        <v>83.34999999999999</v>
+        <v>83.35</v>
       </c>
       <c r="G411" s="5" t="n">
         <v>90013</v>
@@ -10852,7 +10858,7 @@
         <v>40</v>
       </c>
       <c r="F416" s="9" t="n">
-        <v>84.15000000000001</v>
+        <v>84.15</v>
       </c>
       <c r="G416" s="8" t="n">
         <v>90018</v>
@@ -10877,7 +10883,7 @@
         <v>40</v>
       </c>
       <c r="F417" s="6" t="n">
-        <v>84.68000000000001</v>
+        <v>84.68</v>
       </c>
       <c r="G417" s="5" t="n">
         <v>90019</v>
@@ -10927,7 +10933,7 @@
         <v>40</v>
       </c>
       <c r="F419" s="6" t="n">
-        <v>84.20999999999999</v>
+        <v>84.21</v>
       </c>
       <c r="G419" s="5" t="n">
         <v>90021</v>
@@ -10952,7 +10958,7 @@
         <v>58</v>
       </c>
       <c r="F420" s="9" t="n">
-        <v>87.70999999999999</v>
+        <v>87.71</v>
       </c>
       <c r="G420" s="8" t="n">
         <v>90022</v>
@@ -10977,7 +10983,7 @@
         <v>58</v>
       </c>
       <c r="F421" s="6" t="n">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G421" s="5" t="n">
         <v>90023</v>
@@ -11027,7 +11033,7 @@
         <v>58</v>
       </c>
       <c r="F423" s="6" t="n">
-        <v>87.29000000000001</v>
+        <v>87.29</v>
       </c>
       <c r="G423" s="5" t="n">
         <v>90025</v>
@@ -11102,7 +11108,7 @@
         <v>58</v>
       </c>
       <c r="F426" s="9" t="n">
-        <v>87.73999999999999</v>
+        <v>87.74</v>
       </c>
       <c r="G426" s="8" t="n">
         <v>90028</v>
@@ -11152,7 +11158,7 @@
         <v>58</v>
       </c>
       <c r="F428" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G428" s="8" t="n">
         <v>90030</v>
@@ -11243,7 +11249,7 @@
         <v>34</v>
       </c>
       <c r="C432" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D432" s="8" t="n">
         <v>14.24</v>
@@ -11302,7 +11308,7 @@
         <v>73</v>
       </c>
       <c r="F434" s="9" t="n">
-        <v>91.26000000000001</v>
+        <v>91.26</v>
       </c>
       <c r="G434" s="8" t="n">
         <v>90036</v>
@@ -11321,7 +11327,7 @@
         <v>14.24</v>
       </c>
       <c r="D435" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E435" s="5" t="n">
         <v>73</v>
@@ -11346,7 +11352,7 @@
         <v>-14.24</v>
       </c>
       <c r="D436" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E436" s="8" t="n">
         <v>73</v>
@@ -11377,7 +11383,7 @@
         <v>73</v>
       </c>
       <c r="F437" s="6" t="n">
-        <v>90.73999999999999</v>
+        <v>90.74</v>
       </c>
       <c r="G437" s="5" t="n">
         <v>90039</v>
@@ -11402,7 +11408,7 @@
         <v>73</v>
       </c>
       <c r="F438" s="9" t="n">
-        <v>89.95999999999999</v>
+        <v>89.96</v>
       </c>
       <c r="G438" s="8" t="n">
         <v>90040</v>
@@ -11418,7 +11424,7 @@
         <v>41</v>
       </c>
       <c r="C439" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D439" s="5" t="n">
         <v>14.24</v>
@@ -11443,7 +11449,7 @@
         <v>42</v>
       </c>
       <c r="C440" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D440" s="8" t="n">
         <v>-14.24</v>
@@ -11502,7 +11508,7 @@
         <v>73</v>
       </c>
       <c r="F442" s="9" t="n">
-        <v>89.98999999999999</v>
+        <v>89.99</v>
       </c>
       <c r="G442" s="8" t="n">
         <v>90044</v>
@@ -11521,7 +11527,7 @@
         <v>-14.24</v>
       </c>
       <c r="D443" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E443" s="5" t="n">
         <v>73</v>
@@ -11546,7 +11552,7 @@
         <v>14.24</v>
       </c>
       <c r="D444" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E444" s="8" t="n">
         <v>73</v>
@@ -11602,7 +11608,7 @@
         <v>73</v>
       </c>
       <c r="F446" s="9" t="n">
-        <v>90.31999999999999</v>
+        <v>90.32</v>
       </c>
       <c r="G446" s="8" t="n">
         <v>90048</v>
@@ -11618,7 +11624,7 @@
         <v>49</v>
       </c>
       <c r="C447" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D447" s="5" t="n">
         <v>-14.24</v>
@@ -11677,7 +11683,7 @@
         <v>22</v>
       </c>
       <c r="F449" s="6" t="n">
-        <v>83.93000000000001</v>
+        <v>83.93</v>
       </c>
       <c r="G449" s="5" t="n">
         <v>100002</v>
@@ -11852,7 +11858,7 @@
         <v>22</v>
       </c>
       <c r="F456" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.1</v>
       </c>
       <c r="G456" s="8" t="n">
         <v>100009</v>
@@ -11877,7 +11883,7 @@
         <v>40</v>
       </c>
       <c r="F457" s="6" t="n">
-        <v>85.84999999999999</v>
+        <v>85.85</v>
       </c>
       <c r="G457" s="5" t="n">
         <v>100010</v>
@@ -11927,7 +11933,7 @@
         <v>40</v>
       </c>
       <c r="F459" s="6" t="n">
-        <v>85.51000000000001</v>
+        <v>85.51</v>
       </c>
       <c r="G459" s="5" t="n">
         <v>100012</v>
@@ -11952,7 +11958,7 @@
         <v>40</v>
       </c>
       <c r="F460" s="9" t="n">
-        <v>86.29000000000001</v>
+        <v>86.29</v>
       </c>
       <c r="G460" s="8" t="n">
         <v>100013</v>
@@ -12227,7 +12233,7 @@
         <v>58</v>
       </c>
       <c r="F471" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.9</v>
       </c>
       <c r="G471" s="5" t="n">
         <v>100024</v>
@@ -12302,7 +12308,7 @@
         <v>58</v>
       </c>
       <c r="F474" s="9" t="n">
-        <v>89.29000000000001</v>
+        <v>89.29</v>
       </c>
       <c r="G474" s="8" t="n">
         <v>100027</v>
@@ -12352,7 +12358,7 @@
         <v>58</v>
       </c>
       <c r="F476" s="9" t="n">
-        <v>89.40000000000001</v>
+        <v>89.4</v>
       </c>
       <c r="G476" s="8" t="n">
         <v>100029</v>
@@ -12452,7 +12458,7 @@
         <v>58</v>
       </c>
       <c r="F480" s="9" t="n">
-        <v>88.65000000000001</v>
+        <v>88.65</v>
       </c>
       <c r="G480" s="8" t="n">
         <v>100033</v>
@@ -12468,7 +12474,7 @@
         <v>34</v>
       </c>
       <c r="C481" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D481" s="5" t="n">
         <v>14.24</v>
@@ -12477,7 +12483,7 @@
         <v>73</v>
       </c>
       <c r="F481" s="6" t="n">
-        <v>92.31999999999999</v>
+        <v>92.32</v>
       </c>
       <c r="G481" s="5" t="n">
         <v>100034</v>
@@ -12502,7 +12508,7 @@
         <v>73</v>
       </c>
       <c r="F482" s="9" t="n">
-        <v>92.76000000000001</v>
+        <v>92.76</v>
       </c>
       <c r="G482" s="8" t="n">
         <v>100035</v>
@@ -12546,7 +12552,7 @@
         <v>14.24</v>
       </c>
       <c r="D484" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E484" s="8" t="n">
         <v>73</v>
@@ -12571,7 +12577,7 @@
         <v>-14.24</v>
       </c>
       <c r="D485" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E485" s="5" t="n">
         <v>73</v>
@@ -12643,7 +12649,7 @@
         <v>41</v>
       </c>
       <c r="C488" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D488" s="8" t="n">
         <v>14.24</v>
@@ -12652,7 +12658,7 @@
         <v>73</v>
       </c>
       <c r="F488" s="9" t="n">
-        <v>92.26000000000001</v>
+        <v>92.26</v>
       </c>
       <c r="G488" s="8" t="n">
         <v>100041</v>
@@ -12668,7 +12674,7 @@
         <v>42</v>
       </c>
       <c r="C489" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D489" s="5" t="n">
         <v>-14.24</v>
@@ -12746,13 +12752,13 @@
         <v>-14.24</v>
       </c>
       <c r="D492" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E492" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F492" s="9" t="n">
-        <v>91.84999999999999</v>
+        <v>91.85</v>
       </c>
       <c r="G492" s="8" t="n">
         <v>100045</v>
@@ -12771,7 +12777,7 @@
         <v>14.24</v>
       </c>
       <c r="D493" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E493" s="5" t="n">
         <v>73</v>
@@ -12802,7 +12808,7 @@
         <v>73</v>
       </c>
       <c r="F494" s="9" t="n">
-        <v>91.90000000000001</v>
+        <v>91.9</v>
       </c>
       <c r="G494" s="8" t="n">
         <v>100047</v>
@@ -12843,7 +12849,7 @@
         <v>49</v>
       </c>
       <c r="C496" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D496" s="8" t="n">
         <v>-14.24</v>
@@ -12852,7 +12858,7 @@
         <v>73</v>
       </c>
       <c r="F496" s="9" t="n">
-        <v>92.98999999999999</v>
+        <v>92.99</v>
       </c>
       <c r="G496" s="8" t="n">
         <v>100049</v>
@@ -12877,7 +12883,7 @@
         <v>0</v>
       </c>
       <c r="F497" s="6" t="n">
-        <v>82.29000000000001</v>
+        <v>82.29</v>
       </c>
       <c r="G497" s="5" t="n">
         <v>110001</v>
@@ -12902,7 +12908,7 @@
         <v>22</v>
       </c>
       <c r="F498" s="9" t="n">
-        <v>82.15000000000001</v>
+        <v>82.15</v>
       </c>
       <c r="G498" s="8" t="n">
         <v>110002</v>
@@ -12977,7 +12983,7 @@
         <v>22</v>
       </c>
       <c r="F501" s="6" t="n">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="G501" s="5" t="n">
         <v>110005</v>
@@ -13277,7 +13283,7 @@
         <v>40</v>
       </c>
       <c r="F513" s="6" t="n">
-        <v>84.84999999999999</v>
+        <v>84.85</v>
       </c>
       <c r="G513" s="5" t="n">
         <v>110017</v>
@@ -13352,7 +13358,7 @@
         <v>40</v>
       </c>
       <c r="F516" s="9" t="n">
-        <v>84.56999999999999</v>
+        <v>84.57</v>
       </c>
       <c r="G516" s="8" t="n">
         <v>110020</v>
@@ -13427,7 +13433,7 @@
         <v>58</v>
       </c>
       <c r="F519" s="6" t="n">
-        <v>87.65000000000001</v>
+        <v>87.65</v>
       </c>
       <c r="G519" s="5" t="n">
         <v>110023</v>
@@ -13502,7 +13508,7 @@
         <v>58</v>
       </c>
       <c r="F522" s="9" t="n">
-        <v>88.34999999999999</v>
+        <v>88.35</v>
       </c>
       <c r="G522" s="8" t="n">
         <v>110026</v>
@@ -13602,7 +13608,7 @@
         <v>58</v>
       </c>
       <c r="F526" s="9" t="n">
-        <v>87.23999999999999</v>
+        <v>87.24</v>
       </c>
       <c r="G526" s="8" t="n">
         <v>110030</v>
@@ -13677,7 +13683,7 @@
         <v>58</v>
       </c>
       <c r="F529" s="6" t="n">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G529" s="5" t="n">
         <v>110033</v>
@@ -13693,7 +13699,7 @@
         <v>34</v>
       </c>
       <c r="C530" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D530" s="8" t="n">
         <v>14.24</v>
@@ -13771,7 +13777,7 @@
         <v>14.24</v>
       </c>
       <c r="D533" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E533" s="5" t="n">
         <v>73</v>
@@ -13796,13 +13802,13 @@
         <v>-14.24</v>
       </c>
       <c r="D534" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E534" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F534" s="9" t="n">
-        <v>92.15000000000001</v>
+        <v>92.15</v>
       </c>
       <c r="G534" s="8" t="n">
         <v>110038</v>
@@ -13827,7 +13833,7 @@
         <v>73</v>
       </c>
       <c r="F535" s="6" t="n">
-        <v>92.09999999999999</v>
+        <v>92.1</v>
       </c>
       <c r="G535" s="5" t="n">
         <v>110039</v>
@@ -13868,7 +13874,7 @@
         <v>41</v>
       </c>
       <c r="C537" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D537" s="5" t="n">
         <v>14.24</v>
@@ -13877,7 +13883,7 @@
         <v>73</v>
       </c>
       <c r="F537" s="6" t="n">
-        <v>91.40000000000001</v>
+        <v>91.4</v>
       </c>
       <c r="G537" s="5" t="n">
         <v>110041</v>
@@ -13893,7 +13899,7 @@
         <v>42</v>
       </c>
       <c r="C538" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D538" s="8" t="n">
         <v>-14.24</v>
@@ -13971,13 +13977,13 @@
         <v>-14.24</v>
       </c>
       <c r="D541" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E541" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F541" s="6" t="n">
-        <v>90.84999999999999</v>
+        <v>90.85</v>
       </c>
       <c r="G541" s="5" t="n">
         <v>110045</v>
@@ -13996,7 +14002,7 @@
         <v>14.24</v>
       </c>
       <c r="D542" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E542" s="8" t="n">
         <v>73</v>
@@ -14068,7 +14074,7 @@
         <v>49</v>
       </c>
       <c r="C545" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D545" s="5" t="n">
         <v>-14.24</v>
@@ -14202,7 +14208,7 @@
         <v>22</v>
       </c>
       <c r="F550" s="9" t="n">
-        <v>89.90000000000001</v>
+        <v>89.9</v>
       </c>
       <c r="G550" s="8" t="n">
         <v>120005</v>
@@ -14352,7 +14358,7 @@
         <v>40</v>
       </c>
       <c r="F556" s="9" t="n">
-        <v>84.76000000000001</v>
+        <v>84.76</v>
       </c>
       <c r="G556" s="8" t="n">
         <v>120011</v>
@@ -14427,7 +14433,7 @@
         <v>40</v>
       </c>
       <c r="F559" s="6" t="n">
-        <v>84.65000000000001</v>
+        <v>84.65</v>
       </c>
       <c r="G559" s="5" t="n">
         <v>120014</v>
@@ -14577,7 +14583,7 @@
         <v>40</v>
       </c>
       <c r="F565" s="6" t="n">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="G565" s="5" t="n">
         <v>120020</v>
@@ -14627,7 +14633,7 @@
         <v>58</v>
       </c>
       <c r="F567" s="6" t="n">
-        <v>87.51000000000001</v>
+        <v>87.51</v>
       </c>
       <c r="G567" s="5" t="n">
         <v>120022</v>
@@ -14652,7 +14658,7 @@
         <v>58</v>
       </c>
       <c r="F568" s="9" t="n">
-        <v>87.45999999999999</v>
+        <v>87.46</v>
       </c>
       <c r="G568" s="8" t="n">
         <v>120023</v>
@@ -14827,7 +14833,7 @@
         <v>58</v>
       </c>
       <c r="F575" s="6" t="n">
-        <v>87.48999999999999</v>
+        <v>87.49</v>
       </c>
       <c r="G575" s="5" t="n">
         <v>120030</v>
@@ -14902,7 +14908,7 @@
         <v>58</v>
       </c>
       <c r="F578" s="9" t="n">
-        <v>87.98999999999999</v>
+        <v>87.99</v>
       </c>
       <c r="G578" s="8" t="n">
         <v>120033</v>
@@ -14918,7 +14924,7 @@
         <v>34</v>
       </c>
       <c r="C579" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D579" s="5" t="n">
         <v>14.24</v>
@@ -14927,7 +14933,7 @@
         <v>73</v>
       </c>
       <c r="F579" s="6" t="n">
-        <v>90.95999999999999</v>
+        <v>90.96</v>
       </c>
       <c r="G579" s="5" t="n">
         <v>120034</v>
@@ -14952,7 +14958,7 @@
         <v>73</v>
       </c>
       <c r="F580" s="9" t="n">
-        <v>90.68000000000001</v>
+        <v>90.68</v>
       </c>
       <c r="G580" s="8" t="n">
         <v>120035</v>
@@ -14996,7 +15002,7 @@
         <v>14.24</v>
       </c>
       <c r="D582" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E582" s="8" t="n">
         <v>73</v>
@@ -15021,7 +15027,7 @@
         <v>-14.24</v>
       </c>
       <c r="D583" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E583" s="5" t="n">
         <v>73</v>
@@ -15077,7 +15083,7 @@
         <v>73</v>
       </c>
       <c r="F585" s="6" t="n">
-        <v>90.70999999999999</v>
+        <v>90.71</v>
       </c>
       <c r="G585" s="5" t="n">
         <v>120040</v>
@@ -15093,7 +15099,7 @@
         <v>41</v>
       </c>
       <c r="C586" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D586" s="8" t="n">
         <v>14.24</v>
@@ -15102,7 +15108,7 @@
         <v>73</v>
       </c>
       <c r="F586" s="9" t="n">
-        <v>91.65000000000001</v>
+        <v>91.65</v>
       </c>
       <c r="G586" s="8" t="n">
         <v>120041</v>
@@ -15118,7 +15124,7 @@
         <v>42</v>
       </c>
       <c r="C587" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D587" s="5" t="n">
         <v>-14.24</v>
@@ -15177,7 +15183,7 @@
         <v>73</v>
       </c>
       <c r="F589" s="6" t="n">
-        <v>91.65000000000001</v>
+        <v>91.65</v>
       </c>
       <c r="G589" s="5" t="n">
         <v>120044</v>
@@ -15196,7 +15202,7 @@
         <v>-14.24</v>
       </c>
       <c r="D590" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E590" s="8" t="n">
         <v>73</v>
@@ -15221,13 +15227,13 @@
         <v>14.24</v>
       </c>
       <c r="D591" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E591" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F591" s="6" t="n">
-        <v>90.56999999999999</v>
+        <v>90.57</v>
       </c>
       <c r="G591" s="5" t="n">
         <v>120046</v>
@@ -15293,7 +15299,7 @@
         <v>49</v>
       </c>
       <c r="C594" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D594" s="8" t="n">
         <v>-14.24</v>
@@ -15327,7 +15333,7 @@
         <v>22</v>
       </c>
       <c r="F595" s="6" t="n">
-        <v>83.40000000000001</v>
+        <v>83.4</v>
       </c>
       <c r="G595" s="5" t="n">
         <v>125005</v>
@@ -15352,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="F596" s="9" t="n">
-        <v>83.06999999999999</v>
+        <v>83.07</v>
       </c>
       <c r="G596" s="8" t="n">
         <v>130001</v>
@@ -15402,7 +15408,7 @@
         <v>22</v>
       </c>
       <c r="F598" s="9" t="n">
-        <v>84.01000000000001</v>
+        <v>84.01</v>
       </c>
       <c r="G598" s="8" t="n">
         <v>130003</v>
@@ -15477,7 +15483,7 @@
         <v>22</v>
       </c>
       <c r="F601" s="6" t="n">
-        <v>84.04000000000001</v>
+        <v>84.04</v>
       </c>
       <c r="G601" s="5" t="n">
         <v>130006</v>
@@ -15777,7 +15783,7 @@
         <v>40</v>
       </c>
       <c r="F613" s="6" t="n">
-        <v>86.65000000000001</v>
+        <v>86.65</v>
       </c>
       <c r="G613" s="5" t="n">
         <v>130018</v>
@@ -15852,7 +15858,7 @@
         <v>40</v>
       </c>
       <c r="F616" s="9" t="n">
-        <v>86.51000000000001</v>
+        <v>86.51</v>
       </c>
       <c r="G616" s="8" t="n">
         <v>130021</v>
@@ -15877,7 +15883,7 @@
         <v>58</v>
       </c>
       <c r="F617" s="6" t="n">
-        <v>89.06999999999999</v>
+        <v>89.07</v>
       </c>
       <c r="G617" s="5" t="n">
         <v>130022</v>
@@ -15902,7 +15908,7 @@
         <v>58</v>
       </c>
       <c r="F618" s="9" t="n">
-        <v>90.45999999999999</v>
+        <v>90.46</v>
       </c>
       <c r="G618" s="8" t="n">
         <v>130023</v>
@@ -15952,7 +15958,7 @@
         <v>58</v>
       </c>
       <c r="F620" s="9" t="n">
-        <v>89.23999999999999</v>
+        <v>89.24</v>
       </c>
       <c r="G620" s="8" t="n">
         <v>130025</v>
@@ -15977,7 +15983,7 @@
         <v>58</v>
       </c>
       <c r="F621" s="6" t="n">
-        <v>89.68000000000001</v>
+        <v>89.68</v>
       </c>
       <c r="G621" s="5" t="n">
         <v>130026</v>
@@ -16027,7 +16033,7 @@
         <v>58</v>
       </c>
       <c r="F623" s="6" t="n">
-        <v>88.98999999999999</v>
+        <v>88.99</v>
       </c>
       <c r="G623" s="5" t="n">
         <v>130028</v>
@@ -16077,7 +16083,7 @@
         <v>58</v>
       </c>
       <c r="F625" s="6" t="n">
-        <v>89.84999999999999</v>
+        <v>89.85</v>
       </c>
       <c r="G625" s="5" t="n">
         <v>130030</v>
@@ -16168,7 +16174,7 @@
         <v>34</v>
       </c>
       <c r="C629" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D629" s="5" t="n">
         <v>14.24</v>
@@ -16246,7 +16252,7 @@
         <v>14.24</v>
       </c>
       <c r="D632" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E632" s="8" t="n">
         <v>73</v>
@@ -16271,7 +16277,7 @@
         <v>-14.24</v>
       </c>
       <c r="D633" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E633" s="5" t="n">
         <v>73</v>
@@ -16343,7 +16349,7 @@
         <v>41</v>
       </c>
       <c r="C636" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D636" s="8" t="n">
         <v>14.24</v>
@@ -16368,7 +16374,7 @@
         <v>42</v>
       </c>
       <c r="C637" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D637" s="5" t="n">
         <v>-14.24</v>
@@ -16427,7 +16433,7 @@
         <v>73</v>
       </c>
       <c r="F639" s="6" t="n">
-        <v>92.79000000000001</v>
+        <v>92.79</v>
       </c>
       <c r="G639" s="5" t="n">
         <v>130044</v>
@@ -16446,7 +16452,7 @@
         <v>-14.24</v>
       </c>
       <c r="D640" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E640" s="8" t="n">
         <v>73</v>
@@ -16471,7 +16477,7 @@
         <v>14.24</v>
       </c>
       <c r="D641" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E641" s="5" t="n">
         <v>73</v>
@@ -16543,7 +16549,7 @@
         <v>49</v>
       </c>
       <c r="C644" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D644" s="8" t="n">
         <v>-14.24</v>
@@ -16577,7 +16583,7 @@
         <v>0</v>
       </c>
       <c r="F645" s="6" t="n">
-        <v>82.81999999999999</v>
+        <v>82.82</v>
       </c>
       <c r="G645" s="5" t="n">
         <v>140001</v>
@@ -16652,7 +16658,7 @@
         <v>22</v>
       </c>
       <c r="F648" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>83.4</v>
       </c>
       <c r="G648" s="8" t="n">
         <v>140004</v>
@@ -16752,7 +16758,7 @@
         <v>22</v>
       </c>
       <c r="F652" s="9" t="n">
-        <v>83.26000000000001</v>
+        <v>83.26</v>
       </c>
       <c r="G652" s="8" t="n">
         <v>140008</v>
@@ -16952,7 +16958,7 @@
         <v>40</v>
       </c>
       <c r="F660" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="G660" s="8" t="n">
         <v>140016</v>
@@ -16977,7 +16983,7 @@
         <v>40</v>
       </c>
       <c r="F661" s="6" t="n">
-        <v>84.76000000000001</v>
+        <v>84.76</v>
       </c>
       <c r="G661" s="5" t="n">
         <v>140017</v>
@@ -17127,7 +17133,7 @@
         <v>58</v>
       </c>
       <c r="F667" s="6" t="n">
-        <v>87.65000000000001</v>
+        <v>87.65</v>
       </c>
       <c r="G667" s="5" t="n">
         <v>140023</v>
@@ -17152,7 +17158,7 @@
         <v>58</v>
       </c>
       <c r="F668" s="9" t="n">
-        <v>89.15000000000001</v>
+        <v>89.15</v>
       </c>
       <c r="G668" s="8" t="n">
         <v>140024</v>
@@ -17202,7 +17208,7 @@
         <v>58</v>
       </c>
       <c r="F670" s="9" t="n">
-        <v>88.04000000000001</v>
+        <v>88.04</v>
       </c>
       <c r="G670" s="8" t="n">
         <v>140026</v>
@@ -17302,7 +17308,7 @@
         <v>58</v>
       </c>
       <c r="F674" s="9" t="n">
-        <v>88.73999999999999</v>
+        <v>88.74</v>
       </c>
       <c r="G674" s="8" t="n">
         <v>140030</v>
@@ -17377,7 +17383,7 @@
         <v>58</v>
       </c>
       <c r="F677" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.9</v>
       </c>
       <c r="G677" s="5" t="n">
         <v>140033</v>
@@ -17393,7 +17399,7 @@
         <v>34</v>
       </c>
       <c r="C678" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D678" s="8" t="n">
         <v>14.24</v>
@@ -17402,7 +17408,7 @@
         <v>73</v>
       </c>
       <c r="F678" s="9" t="n">
-        <v>91.23999999999999</v>
+        <v>91.24</v>
       </c>
       <c r="G678" s="8" t="n">
         <v>140034</v>
@@ -17471,7 +17477,7 @@
         <v>14.24</v>
       </c>
       <c r="D681" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E681" s="5" t="n">
         <v>73</v>
@@ -17496,13 +17502,13 @@
         <v>-14.24</v>
       </c>
       <c r="D682" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E682" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F682" s="9" t="n">
-        <v>92.29000000000001</v>
+        <v>92.29</v>
       </c>
       <c r="G682" s="8" t="n">
         <v>140038</v>
@@ -17568,7 +17574,7 @@
         <v>41</v>
       </c>
       <c r="C685" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D685" s="5" t="n">
         <v>14.24</v>
@@ -17593,7 +17599,7 @@
         <v>42</v>
       </c>
       <c r="C686" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D686" s="8" t="n">
         <v>-14.24</v>
@@ -17602,7 +17608,7 @@
         <v>73</v>
       </c>
       <c r="F686" s="9" t="n">
-        <v>91.73999999999999</v>
+        <v>91.74</v>
       </c>
       <c r="G686" s="8" t="n">
         <v>140042</v>
@@ -17627,7 +17633,7 @@
         <v>73</v>
       </c>
       <c r="F687" s="6" t="n">
-        <v>92.20999999999999</v>
+        <v>92.21</v>
       </c>
       <c r="G687" s="5" t="n">
         <v>140043</v>
@@ -17671,13 +17677,13 @@
         <v>-14.24</v>
       </c>
       <c r="D689" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E689" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F689" s="6" t="n">
-        <v>92.31999999999999</v>
+        <v>92.32</v>
       </c>
       <c r="G689" s="5" t="n">
         <v>140045</v>
@@ -17696,7 +17702,7 @@
         <v>14.24</v>
       </c>
       <c r="D690" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E690" s="8" t="n">
         <v>73</v>
@@ -17727,7 +17733,7 @@
         <v>73</v>
       </c>
       <c r="F691" s="6" t="n">
-        <v>91.51000000000001</v>
+        <v>91.51</v>
       </c>
       <c r="G691" s="5" t="n">
         <v>140047</v>
@@ -17768,7 +17774,7 @@
         <v>49</v>
       </c>
       <c r="C693" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D693" s="5" t="n">
         <v>-14.24</v>
@@ -17902,7 +17908,7 @@
         <v>22</v>
       </c>
       <c r="F698" s="9" t="n">
-        <v>81.34999999999999</v>
+        <v>81.35</v>
       </c>
       <c r="G698" s="8" t="n">
         <v>150005</v>
@@ -17952,7 +17958,7 @@
         <v>22</v>
       </c>
       <c r="F700" s="9" t="n">
-        <v>81.29000000000001</v>
+        <v>81.29</v>
       </c>
       <c r="G700" s="8" t="n">
         <v>150007</v>
@@ -18002,7 +18008,7 @@
         <v>22</v>
       </c>
       <c r="F702" s="9" t="n">
-        <v>82.48999999999999</v>
+        <v>82.49</v>
       </c>
       <c r="G702" s="8" t="n">
         <v>150009</v>
@@ -18102,7 +18108,7 @@
         <v>40</v>
       </c>
       <c r="F706" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="G706" s="8" t="n">
         <v>150013</v>
@@ -18277,7 +18283,7 @@
         <v>40</v>
       </c>
       <c r="F713" s="6" t="n">
-        <v>84.31999999999999</v>
+        <v>84.32</v>
       </c>
       <c r="G713" s="5" t="n">
         <v>150020</v>
@@ -18377,7 +18383,7 @@
         <v>58</v>
       </c>
       <c r="F717" s="6" t="n">
-        <v>87.09999999999999</v>
+        <v>87.1</v>
       </c>
       <c r="G717" s="5" t="n">
         <v>150024</v>
@@ -18402,7 +18408,7 @@
         <v>58</v>
       </c>
       <c r="F718" s="9" t="n">
-        <v>86.65000000000001</v>
+        <v>86.65</v>
       </c>
       <c r="G718" s="8" t="n">
         <v>150025</v>
@@ -18502,7 +18508,7 @@
         <v>58</v>
       </c>
       <c r="F722" s="9" t="n">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="G722" s="8" t="n">
         <v>150029</v>
@@ -18618,7 +18624,7 @@
         <v>34</v>
       </c>
       <c r="C727" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D727" s="5" t="n">
         <v>14.24</v>
@@ -18696,13 +18702,13 @@
         <v>14.24</v>
       </c>
       <c r="D730" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E730" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F730" s="9" t="n">
-        <v>90.29000000000001</v>
+        <v>90.29</v>
       </c>
       <c r="G730" s="8" t="n">
         <v>150037</v>
@@ -18721,7 +18727,7 @@
         <v>-14.24</v>
       </c>
       <c r="D731" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E731" s="5" t="n">
         <v>73</v>
@@ -18752,7 +18758,7 @@
         <v>73</v>
       </c>
       <c r="F732" s="9" t="n">
-        <v>90.68000000000001</v>
+        <v>90.68</v>
       </c>
       <c r="G732" s="8" t="n">
         <v>150039</v>
@@ -18777,7 +18783,7 @@
         <v>73</v>
       </c>
       <c r="F733" s="6" t="n">
-        <v>90.51000000000001</v>
+        <v>90.51</v>
       </c>
       <c r="G733" s="5" t="n">
         <v>150040</v>
@@ -18793,7 +18799,7 @@
         <v>41</v>
       </c>
       <c r="C734" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D734" s="8" t="n">
         <v>14.24</v>
@@ -18818,7 +18824,7 @@
         <v>42</v>
       </c>
       <c r="C735" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D735" s="5" t="n">
         <v>-14.24</v>
@@ -18827,7 +18833,7 @@
         <v>73</v>
       </c>
       <c r="F735" s="6" t="n">
-        <v>91.15000000000001</v>
+        <v>91.15</v>
       </c>
       <c r="G735" s="5" t="n">
         <v>150042</v>
@@ -18852,7 +18858,7 @@
         <v>73</v>
       </c>
       <c r="F736" s="9" t="n">
-        <v>90.70999999999999</v>
+        <v>90.71</v>
       </c>
       <c r="G736" s="8" t="n">
         <v>150043</v>
@@ -18896,7 +18902,7 @@
         <v>-14.24</v>
       </c>
       <c r="D738" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E738" s="8" t="n">
         <v>73</v>
@@ -18921,13 +18927,13 @@
         <v>14.24</v>
       </c>
       <c r="D739" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E739" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F739" s="6" t="n">
-        <v>90.81999999999999</v>
+        <v>90.82</v>
       </c>
       <c r="G739" s="5" t="n">
         <v>150046</v>
@@ -18977,7 +18983,7 @@
         <v>73</v>
       </c>
       <c r="F741" s="6" t="n">
-        <v>90.29000000000001</v>
+        <v>90.29</v>
       </c>
       <c r="G741" s="5" t="n">
         <v>150048</v>
@@ -18993,7 +18999,7 @@
         <v>49</v>
       </c>
       <c r="C742" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D742" s="8" t="n">
         <v>-14.24</v>
@@ -19002,7 +19008,7 @@
         <v>73</v>
       </c>
       <c r="F742" s="9" t="n">
-        <v>90.56999999999999</v>
+        <v>90.57</v>
       </c>
       <c r="G742" s="8" t="n">
         <v>150049</v>
@@ -19077,7 +19083,7 @@
         <v>22</v>
       </c>
       <c r="F745" s="6" t="n">
-        <v>83.45999999999999</v>
+        <v>83.46</v>
       </c>
       <c r="G745" s="5" t="n">
         <v>160003</v>
@@ -19102,7 +19108,7 @@
         <v>22</v>
       </c>
       <c r="F746" s="9" t="n">
-        <v>82.81999999999999</v>
+        <v>82.82</v>
       </c>
       <c r="G746" s="8" t="n">
         <v>160004</v>
@@ -19127,7 +19133,7 @@
         <v>22</v>
       </c>
       <c r="F747" s="6" t="n">
-        <v>82.29000000000001</v>
+        <v>82.29</v>
       </c>
       <c r="G747" s="5" t="n">
         <v>160005</v>
@@ -19177,7 +19183,7 @@
         <v>22</v>
       </c>
       <c r="F749" s="6" t="n">
-        <v>82.29000000000001</v>
+        <v>82.29</v>
       </c>
       <c r="G749" s="5" t="n">
         <v>160007</v>
@@ -19202,7 +19208,7 @@
         <v>22</v>
       </c>
       <c r="F750" s="9" t="n">
-        <v>83.01000000000001</v>
+        <v>83.01</v>
       </c>
       <c r="G750" s="8" t="n">
         <v>160008</v>
@@ -19302,7 +19308,7 @@
         <v>40</v>
       </c>
       <c r="F754" s="9" t="n">
-        <v>85.43000000000001</v>
+        <v>85.43</v>
       </c>
       <c r="G754" s="8" t="n">
         <v>160012</v>
@@ -19352,7 +19358,7 @@
         <v>40</v>
       </c>
       <c r="F756" s="9" t="n">
-        <v>83.93000000000001</v>
+        <v>83.93</v>
       </c>
       <c r="G756" s="8" t="n">
         <v>160014</v>
@@ -19502,7 +19508,7 @@
         <v>40</v>
       </c>
       <c r="F762" s="9" t="n">
-        <v>85.18000000000001</v>
+        <v>85.18</v>
       </c>
       <c r="G762" s="8" t="n">
         <v>160020</v>
@@ -19527,7 +19533,7 @@
         <v>40</v>
       </c>
       <c r="F763" s="6" t="n">
-        <v>84.15000000000001</v>
+        <v>84.15</v>
       </c>
       <c r="G763" s="5" t="n">
         <v>160021</v>
@@ -19577,7 +19583,7 @@
         <v>58</v>
       </c>
       <c r="F765" s="6" t="n">
-        <v>88.43000000000001</v>
+        <v>88.43</v>
       </c>
       <c r="G765" s="5" t="n">
         <v>160023</v>
@@ -19602,7 +19608,7 @@
         <v>58</v>
       </c>
       <c r="F766" s="9" t="n">
-        <v>88.06999999999999</v>
+        <v>88.07</v>
       </c>
       <c r="G766" s="8" t="n">
         <v>160024</v>
@@ -19652,7 +19658,7 @@
         <v>58</v>
       </c>
       <c r="F768" s="9" t="n">
-        <v>87.56999999999999</v>
+        <v>87.57</v>
       </c>
       <c r="G768" s="8" t="n">
         <v>160026</v>
@@ -19802,7 +19808,7 @@
         <v>58</v>
       </c>
       <c r="F774" s="9" t="n">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="G774" s="8" t="n">
         <v>160032</v>
@@ -19843,7 +19849,7 @@
         <v>34</v>
       </c>
       <c r="C776" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D776" s="8" t="n">
         <v>14.24</v>
@@ -19852,7 +19858,7 @@
         <v>73</v>
       </c>
       <c r="F776" s="9" t="n">
-        <v>91.23999999999999</v>
+        <v>91.24</v>
       </c>
       <c r="G776" s="8" t="n">
         <v>160034</v>
@@ -19921,7 +19927,7 @@
         <v>14.24</v>
       </c>
       <c r="D779" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E779" s="5" t="n">
         <v>73</v>
@@ -19946,7 +19952,7 @@
         <v>-14.24</v>
       </c>
       <c r="D780" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E780" s="8" t="n">
         <v>73</v>
@@ -19977,7 +19983,7 @@
         <v>73</v>
       </c>
       <c r="F781" s="6" t="n">
-        <v>91.06999999999999</v>
+        <v>91.07</v>
       </c>
       <c r="G781" s="5" t="n">
         <v>160039</v>
@@ -20018,7 +20024,7 @@
         <v>41</v>
       </c>
       <c r="C783" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D783" s="5" t="n">
         <v>14.24</v>
@@ -20043,7 +20049,7 @@
         <v>42</v>
       </c>
       <c r="C784" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D784" s="8" t="n">
         <v>-14.24</v>
@@ -20077,7 +20083,7 @@
         <v>73</v>
       </c>
       <c r="F785" s="6" t="n">
-        <v>90.93000000000001</v>
+        <v>90.93</v>
       </c>
       <c r="G785" s="5" t="n">
         <v>160043</v>
@@ -20102,7 +20108,7 @@
         <v>73</v>
       </c>
       <c r="F786" s="9" t="n">
-        <v>91.73999999999999</v>
+        <v>91.74</v>
       </c>
       <c r="G786" s="8" t="n">
         <v>160044</v>
@@ -20121,7 +20127,7 @@
         <v>-14.24</v>
       </c>
       <c r="D787" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E787" s="5" t="n">
         <v>73</v>
@@ -20146,7 +20152,7 @@
         <v>14.24</v>
       </c>
       <c r="D788" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E788" s="8" t="n">
         <v>73</v>
@@ -20177,7 +20183,7 @@
         <v>73</v>
       </c>
       <c r="F789" s="6" t="n">
-        <v>91.73999999999999</v>
+        <v>91.74</v>
       </c>
       <c r="G789" s="5" t="n">
         <v>160047</v>
@@ -20202,7 +20208,7 @@
         <v>73</v>
       </c>
       <c r="F790" s="9" t="n">
-        <v>91.26000000000001</v>
+        <v>91.26</v>
       </c>
       <c r="G790" s="8" t="n">
         <v>160048</v>
@@ -20218,7 +20224,7 @@
         <v>49</v>
       </c>
       <c r="C791" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D791" s="5" t="n">
         <v>-14.24</v>
@@ -20277,7 +20283,7 @@
         <v>22</v>
       </c>
       <c r="F793" s="6" t="n">
-        <v>83.70999999999999</v>
+        <v>83.71</v>
       </c>
       <c r="G793" s="5" t="n">
         <v>170002</v>
@@ -20302,7 +20308,7 @@
         <v>22</v>
       </c>
       <c r="F794" s="9" t="n">
-        <v>83.26000000000001</v>
+        <v>83.26</v>
       </c>
       <c r="G794" s="8" t="n">
         <v>170003</v>
@@ -20352,7 +20358,7 @@
         <v>22</v>
       </c>
       <c r="F796" s="9" t="n">
-        <v>83.56999999999999</v>
+        <v>83.57</v>
       </c>
       <c r="G796" s="8" t="n">
         <v>170005</v>
@@ -20402,7 +20408,7 @@
         <v>22</v>
       </c>
       <c r="F798" s="9" t="n">
-        <v>82.43000000000001</v>
+        <v>82.43</v>
       </c>
       <c r="G798" s="8" t="n">
         <v>170007</v>
@@ -20452,7 +20458,7 @@
         <v>22</v>
       </c>
       <c r="F800" s="9" t="n">
-        <v>83.18000000000001</v>
+        <v>83.18</v>
       </c>
       <c r="G800" s="8" t="n">
         <v>170009</v>
@@ -20602,7 +20608,7 @@
         <v>40</v>
       </c>
       <c r="F806" s="9" t="n">
-        <v>85.73999999999999</v>
+        <v>85.74</v>
       </c>
       <c r="G806" s="8" t="n">
         <v>170015</v>
@@ -20627,7 +20633,7 @@
         <v>40</v>
       </c>
       <c r="F807" s="6" t="n">
-        <v>85.09999999999999</v>
+        <v>85.1</v>
       </c>
       <c r="G807" s="5" t="n">
         <v>170016</v>
@@ -20652,7 +20658,7 @@
         <v>40</v>
       </c>
       <c r="F808" s="9" t="n">
-        <v>84.84999999999999</v>
+        <v>84.85</v>
       </c>
       <c r="G808" s="8" t="n">
         <v>170017</v>
@@ -20677,7 +20683,7 @@
         <v>40</v>
       </c>
       <c r="F809" s="6" t="n">
-        <v>84.73999999999999</v>
+        <v>84.74</v>
       </c>
       <c r="G809" s="5" t="n">
         <v>170018</v>
@@ -20727,7 +20733,7 @@
         <v>40</v>
       </c>
       <c r="F811" s="6" t="n">
-        <v>85.81999999999999</v>
+        <v>85.82</v>
       </c>
       <c r="G811" s="5" t="n">
         <v>170020</v>
@@ -20827,7 +20833,7 @@
         <v>58</v>
       </c>
       <c r="F815" s="6" t="n">
-        <v>88.73999999999999</v>
+        <v>88.74</v>
       </c>
       <c r="G815" s="5" t="n">
         <v>170024</v>
@@ -21068,7 +21074,7 @@
         <v>34</v>
       </c>
       <c r="C825" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D825" s="5" t="n">
         <v>14.24</v>
@@ -21146,7 +21152,7 @@
         <v>14.24</v>
       </c>
       <c r="D828" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E828" s="8" t="n">
         <v>73</v>
@@ -21171,7 +21177,7 @@
         <v>-14.24</v>
       </c>
       <c r="D829" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E829" s="5" t="n">
         <v>73</v>
@@ -21243,7 +21249,7 @@
         <v>41</v>
       </c>
       <c r="C832" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D832" s="8" t="n">
         <v>14.24</v>
@@ -21268,7 +21274,7 @@
         <v>42</v>
       </c>
       <c r="C833" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D833" s="5" t="n">
         <v>-14.24</v>
@@ -21346,7 +21352,7 @@
         <v>-14.24</v>
       </c>
       <c r="D836" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E836" s="8" t="n">
         <v>73</v>
@@ -21371,13 +21377,13 @@
         <v>14.24</v>
       </c>
       <c r="D837" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E837" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F837" s="6" t="n">
-        <v>92.01000000000001</v>
+        <v>92.01</v>
       </c>
       <c r="G837" s="5" t="n">
         <v>170046</v>
@@ -21443,7 +21449,7 @@
         <v>49</v>
       </c>
       <c r="C840" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D840" s="8" t="n">
         <v>-14.24</v>
@@ -21502,7 +21508,7 @@
         <v>22</v>
       </c>
       <c r="F842" s="9" t="n">
-        <v>82.09999999999999</v>
+        <v>82.1</v>
       </c>
       <c r="G842" s="8" t="n">
         <v>180002</v>
@@ -21552,7 +21558,7 @@
         <v>22</v>
       </c>
       <c r="F844" s="9" t="n">
-        <v>82.51000000000001</v>
+        <v>82.51</v>
       </c>
       <c r="G844" s="8" t="n">
         <v>180004</v>
@@ -21677,7 +21683,7 @@
         <v>22</v>
       </c>
       <c r="F849" s="6" t="n">
-        <v>82.70999999999999</v>
+        <v>82.71</v>
       </c>
       <c r="G849" s="5" t="n">
         <v>180009</v>
@@ -21952,7 +21958,7 @@
         <v>40</v>
       </c>
       <c r="F860" s="9" t="n">
-        <v>84.20999999999999</v>
+        <v>84.21</v>
       </c>
       <c r="G860" s="8" t="n">
         <v>180020</v>
@@ -21977,7 +21983,7 @@
         <v>40</v>
       </c>
       <c r="F861" s="6" t="n">
-        <v>85.51000000000001</v>
+        <v>85.51</v>
       </c>
       <c r="G861" s="5" t="n">
         <v>180021</v>
@@ -22293,7 +22299,7 @@
         <v>34</v>
       </c>
       <c r="C874" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D874" s="8" t="n">
         <v>14.24</v>
@@ -22371,13 +22377,13 @@
         <v>14.24</v>
       </c>
       <c r="D877" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E877" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F877" s="6" t="n">
-        <v>90.79000000000001</v>
+        <v>90.79</v>
       </c>
       <c r="G877" s="5" t="n">
         <v>180037</v>
@@ -22396,7 +22402,7 @@
         <v>-14.24</v>
       </c>
       <c r="D878" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E878" s="8" t="n">
         <v>73</v>
@@ -22452,7 +22458,7 @@
         <v>73</v>
       </c>
       <c r="F880" s="9" t="n">
-        <v>91.95999999999999</v>
+        <v>91.96</v>
       </c>
       <c r="G880" s="8" t="n">
         <v>180040</v>
@@ -22468,7 +22474,7 @@
         <v>41</v>
       </c>
       <c r="C881" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D881" s="5" t="n">
         <v>14.24</v>
@@ -22493,7 +22499,7 @@
         <v>42</v>
       </c>
       <c r="C882" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D882" s="8" t="n">
         <v>-14.24</v>
@@ -22552,7 +22558,7 @@
         <v>73</v>
       </c>
       <c r="F884" s="9" t="n">
-        <v>91.65000000000001</v>
+        <v>91.65</v>
       </c>
       <c r="G884" s="8" t="n">
         <v>180044</v>
@@ -22571,13 +22577,13 @@
         <v>-14.24</v>
       </c>
       <c r="D885" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E885" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F885" s="6" t="n">
-        <v>92.06999999999999</v>
+        <v>92.07</v>
       </c>
       <c r="G885" s="5" t="n">
         <v>180045</v>
@@ -22596,13 +22602,13 @@
         <v>14.24</v>
       </c>
       <c r="D886" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E886" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F886" s="9" t="n">
-        <v>92.06999999999999</v>
+        <v>92.07</v>
       </c>
       <c r="G886" s="8" t="n">
         <v>180046</v>
@@ -22668,7 +22674,7 @@
         <v>49</v>
       </c>
       <c r="C889" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D889" s="5" t="n">
         <v>-14.24</v>
@@ -22702,7 +22708,7 @@
         <v>0</v>
       </c>
       <c r="F890" s="9" t="n">
-        <v>80.48999999999999</v>
+        <v>80.49</v>
       </c>
       <c r="G890" s="8" t="n">
         <v>190001</v>
@@ -22777,7 +22783,7 @@
         <v>22</v>
       </c>
       <c r="F893" s="6" t="n">
-        <v>81.51000000000001</v>
+        <v>81.51</v>
       </c>
       <c r="G893" s="5" t="n">
         <v>190004</v>
@@ -22927,7 +22933,7 @@
         <v>40</v>
       </c>
       <c r="F899" s="6" t="n">
-        <v>83.56999999999999</v>
+        <v>83.57</v>
       </c>
       <c r="G899" s="5" t="n">
         <v>190010</v>
@@ -23377,7 +23383,7 @@
         <v>58</v>
       </c>
       <c r="F917" s="6" t="n">
-        <v>86.09999999999999</v>
+        <v>86.1</v>
       </c>
       <c r="G917" s="5" t="n">
         <v>190028</v>
@@ -23518,7 +23524,7 @@
         <v>34</v>
       </c>
       <c r="C923" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D923" s="5" t="n">
         <v>14.24</v>
@@ -23527,7 +23533,7 @@
         <v>73</v>
       </c>
       <c r="F923" s="6" t="n">
-        <v>89.56999999999999</v>
+        <v>89.57</v>
       </c>
       <c r="G923" s="5" t="n">
         <v>190034</v>
@@ -23552,7 +23558,7 @@
         <v>73</v>
       </c>
       <c r="F924" s="9" t="n">
-        <v>90.43000000000001</v>
+        <v>90.43</v>
       </c>
       <c r="G924" s="8" t="n">
         <v>190035</v>
@@ -23596,13 +23602,13 @@
         <v>14.24</v>
       </c>
       <c r="D926" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E926" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F926" s="9" t="n">
-        <v>90.93000000000001</v>
+        <v>90.93</v>
       </c>
       <c r="G926" s="8" t="n">
         <v>190037</v>
@@ -23621,13 +23627,13 @@
         <v>-14.24</v>
       </c>
       <c r="D927" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E927" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F927" s="6" t="n">
-        <v>90.06999999999999</v>
+        <v>90.07</v>
       </c>
       <c r="G927" s="5" t="n">
         <v>190038</v>
@@ -23652,7 +23658,7 @@
         <v>73</v>
       </c>
       <c r="F928" s="9" t="n">
-        <v>89.45999999999999</v>
+        <v>89.46</v>
       </c>
       <c r="G928" s="8" t="n">
         <v>190039</v>
@@ -23693,7 +23699,7 @@
         <v>41</v>
       </c>
       <c r="C930" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D930" s="8" t="n">
         <v>14.24</v>
@@ -23718,7 +23724,7 @@
         <v>42</v>
       </c>
       <c r="C931" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D931" s="5" t="n">
         <v>-14.24</v>
@@ -23752,7 +23758,7 @@
         <v>73</v>
       </c>
       <c r="F932" s="9" t="n">
-        <v>89.59999999999999</v>
+        <v>89.6</v>
       </c>
       <c r="G932" s="8" t="n">
         <v>190043</v>
@@ -23796,13 +23802,13 @@
         <v>-14.24</v>
       </c>
       <c r="D934" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E934" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F934" s="9" t="n">
-        <v>89.54000000000001</v>
+        <v>89.54</v>
       </c>
       <c r="G934" s="8" t="n">
         <v>190045</v>
@@ -23821,7 +23827,7 @@
         <v>14.24</v>
       </c>
       <c r="D935" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E935" s="5" t="n">
         <v>73</v>
@@ -23852,7 +23858,7 @@
         <v>73</v>
       </c>
       <c r="F936" s="9" t="n">
-        <v>89.48999999999999</v>
+        <v>89.49</v>
       </c>
       <c r="G936" s="8" t="n">
         <v>190047</v>
@@ -23893,7 +23899,7 @@
         <v>49</v>
       </c>
       <c r="C938" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D938" s="8" t="n">
         <v>-14.24</v>
@@ -23952,7 +23958,7 @@
         <v>0</v>
       </c>
       <c r="F940" s="9" t="n">
-        <v>81.79000000000001</v>
+        <v>81.79</v>
       </c>
       <c r="G940" s="8" t="n">
         <v>200001</v>
@@ -24027,7 +24033,7 @@
         <v>22</v>
       </c>
       <c r="F943" s="6" t="n">
-        <v>82.51000000000001</v>
+        <v>82.51</v>
       </c>
       <c r="G943" s="5" t="n">
         <v>200004</v>
@@ -24052,7 +24058,7 @@
         <v>22</v>
       </c>
       <c r="F944" s="9" t="n">
-        <v>81.65000000000001</v>
+        <v>81.65</v>
       </c>
       <c r="G944" s="8" t="n">
         <v>200005</v>
@@ -24127,7 +24133,7 @@
         <v>22</v>
       </c>
       <c r="F947" s="6" t="n">
-        <v>82.06999999999999</v>
+        <v>82.07</v>
       </c>
       <c r="G947" s="5" t="n">
         <v>200008</v>
@@ -24277,7 +24283,7 @@
         <v>40</v>
       </c>
       <c r="F953" s="6" t="n">
-        <v>83.76000000000001</v>
+        <v>83.76</v>
       </c>
       <c r="G953" s="5" t="n">
         <v>200014</v>
@@ -24352,7 +24358,7 @@
         <v>40</v>
       </c>
       <c r="F956" s="9" t="n">
-        <v>83.26000000000001</v>
+        <v>83.26</v>
       </c>
       <c r="G956" s="8" t="n">
         <v>200017</v>
@@ -24377,7 +24383,7 @@
         <v>40</v>
       </c>
       <c r="F957" s="6" t="n">
-        <v>84.65000000000001</v>
+        <v>84.65</v>
       </c>
       <c r="G957" s="5" t="n">
         <v>200018</v>
@@ -24452,7 +24458,7 @@
         <v>40</v>
       </c>
       <c r="F960" s="9" t="n">
-        <v>83.26000000000001</v>
+        <v>83.26</v>
       </c>
       <c r="G960" s="8" t="n">
         <v>200021</v>
@@ -24502,7 +24508,7 @@
         <v>58</v>
       </c>
       <c r="F962" s="9" t="n">
-        <v>86.54000000000001</v>
+        <v>86.54</v>
       </c>
       <c r="G962" s="8" t="n">
         <v>200023</v>
@@ -24527,7 +24533,7 @@
         <v>58</v>
       </c>
       <c r="F963" s="6" t="n">
-        <v>86.56999999999999</v>
+        <v>86.57</v>
       </c>
       <c r="G963" s="5" t="n">
         <v>200024</v>
@@ -24577,7 +24583,7 @@
         <v>58</v>
       </c>
       <c r="F965" s="6" t="n">
-        <v>87.20999999999999</v>
+        <v>87.21</v>
       </c>
       <c r="G965" s="5" t="n">
         <v>200026</v>
@@ -24602,7 +24608,7 @@
         <v>58</v>
       </c>
       <c r="F966" s="9" t="n">
-        <v>86.68000000000001</v>
+        <v>86.68</v>
       </c>
       <c r="G966" s="8" t="n">
         <v>200027</v>
@@ -24702,7 +24708,7 @@
         <v>58</v>
       </c>
       <c r="F970" s="9" t="n">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="G970" s="8" t="n">
         <v>200031</v>
@@ -24768,7 +24774,7 @@
         <v>34</v>
       </c>
       <c r="C973" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D973" s="5" t="n">
         <v>14.24</v>
@@ -24777,7 +24783,7 @@
         <v>73</v>
       </c>
       <c r="F973" s="6" t="n">
-        <v>90.26000000000001</v>
+        <v>90.26</v>
       </c>
       <c r="G973" s="5" t="n">
         <v>200034</v>
@@ -24846,7 +24852,7 @@
         <v>14.24</v>
       </c>
       <c r="D976" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E976" s="8" t="n">
         <v>73</v>
@@ -24871,7 +24877,7 @@
         <v>-14.24</v>
       </c>
       <c r="D977" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E977" s="5" t="n">
         <v>73</v>
@@ -24943,7 +24949,7 @@
         <v>41</v>
       </c>
       <c r="C980" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D980" s="8" t="n">
         <v>14.24</v>
@@ -24968,7 +24974,7 @@
         <v>42</v>
       </c>
       <c r="C981" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D981" s="5" t="n">
         <v>-14.24</v>
@@ -25046,7 +25052,7 @@
         <v>-14.24</v>
       </c>
       <c r="D984" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E984" s="8" t="n">
         <v>73</v>
@@ -25071,7 +25077,7 @@
         <v>14.24</v>
       </c>
       <c r="D985" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E985" s="5" t="n">
         <v>73</v>
@@ -25143,7 +25149,7 @@
         <v>49</v>
       </c>
       <c r="C988" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D988" s="8" t="n">
         <v>-14.24</v>
@@ -25152,7 +25158,7 @@
         <v>73</v>
       </c>
       <c r="F988" s="9" t="n">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G988" s="8" t="n">
         <v>200049</v>
@@ -25202,7 +25208,7 @@
         <v>22</v>
       </c>
       <c r="F990" s="9" t="n">
-        <v>82.93000000000001</v>
+        <v>82.93</v>
       </c>
       <c r="G990" s="8" t="n">
         <v>210002</v>
@@ -25277,7 +25283,7 @@
         <v>22</v>
       </c>
       <c r="F993" s="6" t="n">
-        <v>83.26000000000001</v>
+        <v>83.26</v>
       </c>
       <c r="G993" s="5" t="n">
         <v>210005</v>
@@ -25477,7 +25483,7 @@
         <v>40</v>
       </c>
       <c r="F1001" s="6" t="n">
-        <v>84.70999999999999</v>
+        <v>84.71</v>
       </c>
       <c r="G1001" s="5" t="n">
         <v>210013</v>
@@ -25502,7 +25508,7 @@
         <v>40</v>
       </c>
       <c r="F1002" s="9" t="n">
-        <v>85.18000000000001</v>
+        <v>85.18</v>
       </c>
       <c r="G1002" s="8" t="n">
         <v>210014</v>
@@ -25552,7 +25558,7 @@
         <v>40</v>
       </c>
       <c r="F1004" s="9" t="n">
-        <v>85.45999999999999</v>
+        <v>85.46</v>
       </c>
       <c r="G1004" s="8" t="n">
         <v>210016</v>
@@ -25627,7 +25633,7 @@
         <v>40</v>
       </c>
       <c r="F1007" s="6" t="n">
-        <v>85.15000000000001</v>
+        <v>85.15</v>
       </c>
       <c r="G1007" s="5" t="n">
         <v>210019</v>
@@ -25702,7 +25708,7 @@
         <v>58</v>
       </c>
       <c r="F1010" s="9" t="n">
-        <v>88.26000000000001</v>
+        <v>88.26</v>
       </c>
       <c r="G1010" s="8" t="n">
         <v>210022</v>
@@ -25777,7 +25783,7 @@
         <v>58</v>
       </c>
       <c r="F1013" s="6" t="n">
-        <v>87.73999999999999</v>
+        <v>87.74</v>
       </c>
       <c r="G1013" s="5" t="n">
         <v>210025</v>
@@ -25952,7 +25958,7 @@
         <v>58</v>
       </c>
       <c r="F1020" s="9" t="n">
-        <v>87.93000000000001</v>
+        <v>87.93</v>
       </c>
       <c r="G1020" s="8" t="n">
         <v>210032</v>
@@ -25993,7 +25999,7 @@
         <v>34</v>
       </c>
       <c r="C1022" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1022" s="8" t="n">
         <v>14.24</v>
@@ -26071,7 +26077,7 @@
         <v>14.24</v>
       </c>
       <c r="D1025" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1025" s="5" t="n">
         <v>73</v>
@@ -26096,13 +26102,13 @@
         <v>-14.24</v>
       </c>
       <c r="D1026" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1026" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F1026" s="9" t="n">
-        <v>92.29000000000001</v>
+        <v>92.29</v>
       </c>
       <c r="G1026" s="8" t="n">
         <v>210038</v>
@@ -26168,7 +26174,7 @@
         <v>41</v>
       </c>
       <c r="C1029" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1029" s="5" t="n">
         <v>14.24</v>
@@ -26193,7 +26199,7 @@
         <v>42</v>
       </c>
       <c r="C1030" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1030" s="8" t="n">
         <v>-14.24</v>
@@ -26271,7 +26277,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1033" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1033" s="5" t="n">
         <v>73</v>
@@ -26296,13 +26302,13 @@
         <v>14.24</v>
       </c>
       <c r="D1034" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1034" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F1034" s="9" t="n">
-        <v>91.54000000000001</v>
+        <v>91.54</v>
       </c>
       <c r="G1034" s="8" t="n">
         <v>210046</v>
@@ -26368,7 +26374,7 @@
         <v>49</v>
       </c>
       <c r="C1037" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1037" s="5" t="n">
         <v>-14.24</v>
@@ -26652,7 +26658,7 @@
         <v>40</v>
       </c>
       <c r="F1048" s="9" t="n">
-        <v>83.65000000000001</v>
+        <v>83.65</v>
       </c>
       <c r="G1048" s="8" t="n">
         <v>220011</v>
@@ -26702,7 +26708,7 @@
         <v>40</v>
       </c>
       <c r="F1050" s="9" t="n">
-        <v>83.76000000000001</v>
+        <v>83.76</v>
       </c>
       <c r="G1050" s="8" t="n">
         <v>220013</v>
@@ -26752,7 +26758,7 @@
         <v>40</v>
       </c>
       <c r="F1052" s="9" t="n">
-        <v>83.98999999999999</v>
+        <v>83.99</v>
       </c>
       <c r="G1052" s="8" t="n">
         <v>220015</v>
@@ -26802,7 +26808,7 @@
         <v>40</v>
       </c>
       <c r="F1054" s="9" t="n">
-        <v>83.81999999999999</v>
+        <v>83.82</v>
       </c>
       <c r="G1054" s="8" t="n">
         <v>220017</v>
@@ -26827,7 +26833,7 @@
         <v>40</v>
       </c>
       <c r="F1055" s="6" t="n">
-        <v>83.98999999999999</v>
+        <v>83.99</v>
       </c>
       <c r="G1055" s="5" t="n">
         <v>220018</v>
@@ -26877,7 +26883,7 @@
         <v>40</v>
       </c>
       <c r="F1057" s="6" t="n">
-        <v>91.01000000000001</v>
+        <v>91.01</v>
       </c>
       <c r="G1057" s="5" t="n">
         <v>220020</v>
@@ -27052,7 +27058,7 @@
         <v>58</v>
       </c>
       <c r="F1064" s="9" t="n">
-        <v>86.56999999999999</v>
+        <v>86.57</v>
       </c>
       <c r="G1064" s="8" t="n">
         <v>220027</v>
@@ -27102,7 +27108,7 @@
         <v>58</v>
       </c>
       <c r="F1066" s="9" t="n">
-        <v>86.34999999999999</v>
+        <v>86.35</v>
       </c>
       <c r="G1066" s="8" t="n">
         <v>220029</v>
@@ -27152,7 +27158,7 @@
         <v>58</v>
       </c>
       <c r="F1068" s="9" t="n">
-        <v>86.79000000000001</v>
+        <v>86.79</v>
       </c>
       <c r="G1068" s="8" t="n">
         <v>220031</v>
@@ -27218,7 +27224,7 @@
         <v>34</v>
       </c>
       <c r="C1071" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1071" s="5" t="n">
         <v>14.24</v>
@@ -27277,7 +27283,7 @@
         <v>73</v>
       </c>
       <c r="F1073" s="6" t="n">
-        <v>91.23999999999999</v>
+        <v>91.24</v>
       </c>
       <c r="G1073" s="5" t="n">
         <v>220036</v>
@@ -27296,7 +27302,7 @@
         <v>14.24</v>
       </c>
       <c r="D1074" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1074" s="8" t="n">
         <v>73</v>
@@ -27321,7 +27327,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1075" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1075" s="5" t="n">
         <v>73</v>
@@ -27352,7 +27358,7 @@
         <v>73</v>
       </c>
       <c r="F1076" s="9" t="n">
-        <v>90.79000000000001</v>
+        <v>90.79</v>
       </c>
       <c r="G1076" s="8" t="n">
         <v>220039</v>
@@ -27393,7 +27399,7 @@
         <v>41</v>
       </c>
       <c r="C1078" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1078" s="8" t="n">
         <v>14.24</v>
@@ -27418,7 +27424,7 @@
         <v>42</v>
       </c>
       <c r="C1079" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1079" s="5" t="n">
         <v>-14.24</v>
@@ -27496,13 +27502,13 @@
         <v>-14.24</v>
       </c>
       <c r="D1082" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1082" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F1082" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>91.1</v>
       </c>
       <c r="G1082" s="8" t="n">
         <v>220045</v>
@@ -27521,13 +27527,13 @@
         <v>14.24</v>
       </c>
       <c r="D1083" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1083" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F1083" s="6" t="n">
-        <v>90.43000000000001</v>
+        <v>90.43</v>
       </c>
       <c r="G1083" s="5" t="n">
         <v>220046</v>
@@ -27552,7 +27558,7 @@
         <v>73</v>
       </c>
       <c r="F1084" s="9" t="n">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="G1084" s="8" t="n">
         <v>220047</v>
@@ -27593,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="C1086" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1086" s="8" t="n">
         <v>-14.24</v>
@@ -27627,7 +27633,7 @@
         <v>40</v>
       </c>
       <c r="F1087" s="6" t="n">
-        <v>84.51000000000001</v>
+        <v>84.51</v>
       </c>
       <c r="G1087" s="5" t="n">
         <v>225020</v>
@@ -27777,7 +27783,7 @@
         <v>22</v>
       </c>
       <c r="F1093" s="6" t="n">
-        <v>83.95999999999999</v>
+        <v>83.96</v>
       </c>
       <c r="G1093" s="5" t="n">
         <v>230006</v>
@@ -27802,7 +27808,7 @@
         <v>22</v>
       </c>
       <c r="F1094" s="9" t="n">
-        <v>82.70999999999999</v>
+        <v>82.71</v>
       </c>
       <c r="G1094" s="8" t="n">
         <v>230007</v>
@@ -27852,7 +27858,7 @@
         <v>22</v>
       </c>
       <c r="F1096" s="9" t="n">
-        <v>82.95999999999999</v>
+        <v>82.96</v>
       </c>
       <c r="G1096" s="8" t="n">
         <v>230009</v>
@@ -27927,7 +27933,7 @@
         <v>40</v>
       </c>
       <c r="F1099" s="6" t="n">
-        <v>84.70999999999999</v>
+        <v>84.71</v>
       </c>
       <c r="G1099" s="5" t="n">
         <v>230012</v>
@@ -27977,7 +27983,7 @@
         <v>40</v>
       </c>
       <c r="F1101" s="6" t="n">
-        <v>85.23999999999999</v>
+        <v>85.24</v>
       </c>
       <c r="G1101" s="5" t="n">
         <v>230014</v>
@@ -28052,7 +28058,7 @@
         <v>40</v>
       </c>
       <c r="F1104" s="9" t="n">
-        <v>84.51000000000001</v>
+        <v>84.51</v>
       </c>
       <c r="G1104" s="8" t="n">
         <v>230017</v>
@@ -28077,7 +28083,7 @@
         <v>40</v>
       </c>
       <c r="F1105" s="6" t="n">
-        <v>85.70999999999999</v>
+        <v>85.71</v>
       </c>
       <c r="G1105" s="5" t="n">
         <v>230018</v>
@@ -28202,7 +28208,7 @@
         <v>58</v>
       </c>
       <c r="F1110" s="9" t="n">
-        <v>89.04000000000001</v>
+        <v>89.04</v>
       </c>
       <c r="G1110" s="8" t="n">
         <v>230023</v>
@@ -28352,7 +28358,7 @@
         <v>58</v>
       </c>
       <c r="F1116" s="9" t="n">
-        <v>88.48999999999999</v>
+        <v>88.49</v>
       </c>
       <c r="G1116" s="8" t="n">
         <v>230029</v>
@@ -28427,7 +28433,7 @@
         <v>58</v>
       </c>
       <c r="F1119" s="6" t="n">
-        <v>87.70999999999999</v>
+        <v>87.71</v>
       </c>
       <c r="G1119" s="5" t="n">
         <v>230032</v>
@@ -28468,7 +28474,7 @@
         <v>34</v>
       </c>
       <c r="C1121" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1121" s="5" t="n">
         <v>14.24</v>
@@ -28546,7 +28552,7 @@
         <v>14.24</v>
       </c>
       <c r="D1124" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1124" s="8" t="n">
         <v>73</v>
@@ -28571,7 +28577,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1125" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1125" s="5" t="n">
         <v>73</v>
@@ -28602,7 +28608,7 @@
         <v>73</v>
       </c>
       <c r="F1126" s="9" t="n">
-        <v>92.45999999999999</v>
+        <v>92.46</v>
       </c>
       <c r="G1126" s="8" t="n">
         <v>230039</v>
@@ -28627,7 +28633,7 @@
         <v>73</v>
       </c>
       <c r="F1127" s="6" t="n">
-        <v>90.98999999999999</v>
+        <v>90.99</v>
       </c>
       <c r="G1127" s="5" t="n">
         <v>230040</v>
@@ -28643,7 +28649,7 @@
         <v>41</v>
       </c>
       <c r="C1128" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1128" s="8" t="n">
         <v>14.24</v>
@@ -28652,7 +28658,7 @@
         <v>73</v>
       </c>
       <c r="F1128" s="9" t="n">
-        <v>91.81999999999999</v>
+        <v>91.82</v>
       </c>
       <c r="G1128" s="8" t="n">
         <v>230041</v>
@@ -28668,7 +28674,7 @@
         <v>42</v>
       </c>
       <c r="C1129" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1129" s="5" t="n">
         <v>-14.24</v>
@@ -28746,7 +28752,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1132" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1132" s="8" t="n">
         <v>73</v>
@@ -28771,7 +28777,7 @@
         <v>14.24</v>
       </c>
       <c r="D1133" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1133" s="5" t="n">
         <v>73</v>
@@ -28802,7 +28808,7 @@
         <v>73</v>
       </c>
       <c r="F1134" s="9" t="n">
-        <v>92.56999999999999</v>
+        <v>92.57</v>
       </c>
       <c r="G1134" s="8" t="n">
         <v>230047</v>
@@ -28827,7 +28833,7 @@
         <v>73</v>
       </c>
       <c r="F1135" s="6" t="n">
-        <v>91.26000000000001</v>
+        <v>91.26</v>
       </c>
       <c r="G1135" s="5" t="n">
         <v>230048</v>
@@ -28843,7 +28849,7 @@
         <v>49</v>
       </c>
       <c r="C1136" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1136" s="8" t="n">
         <v>-14.24</v>
@@ -28877,7 +28883,7 @@
         <v>0</v>
       </c>
       <c r="F1137" s="6" t="n">
-        <v>83.76000000000001</v>
+        <v>83.76</v>
       </c>
       <c r="G1137" s="5" t="n">
         <v>240001</v>
@@ -28952,7 +28958,7 @@
         <v>22</v>
       </c>
       <c r="F1140" s="9" t="n">
-        <v>84.79000000000001</v>
+        <v>84.79</v>
       </c>
       <c r="G1140" s="8" t="n">
         <v>240004</v>
@@ -29102,7 +29108,7 @@
         <v>40</v>
       </c>
       <c r="F1146" s="9" t="n">
-        <v>85.56999999999999</v>
+        <v>85.57</v>
       </c>
       <c r="G1146" s="8" t="n">
         <v>240010</v>
@@ -29127,7 +29133,7 @@
         <v>40</v>
       </c>
       <c r="F1147" s="6" t="n">
-        <v>86.93000000000001</v>
+        <v>86.93</v>
       </c>
       <c r="G1147" s="5" t="n">
         <v>240011</v>
@@ -29277,7 +29283,7 @@
         <v>40</v>
       </c>
       <c r="F1153" s="6" t="n">
-        <v>86.79000000000001</v>
+        <v>86.79</v>
       </c>
       <c r="G1153" s="5" t="n">
         <v>240017</v>
@@ -29352,7 +29358,7 @@
         <v>40</v>
       </c>
       <c r="F1156" s="9" t="n">
-        <v>86.51000000000001</v>
+        <v>86.51</v>
       </c>
       <c r="G1156" s="8" t="n">
         <v>240020</v>
@@ -29452,7 +29458,7 @@
         <v>58</v>
       </c>
       <c r="F1160" s="9" t="n">
-        <v>89.45999999999999</v>
+        <v>89.46</v>
       </c>
       <c r="G1160" s="8" t="n">
         <v>240024</v>
@@ -29527,7 +29533,7 @@
         <v>58</v>
       </c>
       <c r="F1163" s="6" t="n">
-        <v>89.09999999999999</v>
+        <v>89.1</v>
       </c>
       <c r="G1163" s="5" t="n">
         <v>240027</v>
@@ -29693,7 +29699,7 @@
         <v>34</v>
       </c>
       <c r="C1170" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1170" s="8" t="n">
         <v>14.24</v>
@@ -29702,7 +29708,7 @@
         <v>73</v>
       </c>
       <c r="F1170" s="9" t="n">
-        <v>92.98999999999999</v>
+        <v>92.99</v>
       </c>
       <c r="G1170" s="8" t="n">
         <v>240034</v>
@@ -29752,7 +29758,7 @@
         <v>73</v>
       </c>
       <c r="F1172" s="9" t="n">
-        <v>92.40000000000001</v>
+        <v>92.4</v>
       </c>
       <c r="G1172" s="8" t="n">
         <v>240036</v>
@@ -29771,13 +29777,13 @@
         <v>14.24</v>
       </c>
       <c r="D1173" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1173" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F1173" s="6" t="n">
-        <v>92.26000000000001</v>
+        <v>92.26</v>
       </c>
       <c r="G1173" s="5" t="n">
         <v>240037</v>
@@ -29796,7 +29802,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1174" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1174" s="8" t="n">
         <v>73</v>
@@ -29868,7 +29874,7 @@
         <v>41</v>
       </c>
       <c r="C1177" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1177" s="5" t="n">
         <v>14.24</v>
@@ -29893,7 +29899,7 @@
         <v>42</v>
       </c>
       <c r="C1178" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1178" s="8" t="n">
         <v>-14.24</v>
@@ -29971,7 +29977,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1181" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1181" s="5" t="n">
         <v>73</v>
@@ -29996,13 +30002,13 @@
         <v>14.24</v>
       </c>
       <c r="D1182" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1182" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F1182" s="9" t="n">
-        <v>93.09999999999999</v>
+        <v>93.1</v>
       </c>
       <c r="G1182" s="8" t="n">
         <v>240046</v>
@@ -30068,7 +30074,7 @@
         <v>49</v>
       </c>
       <c r="C1185" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1185" s="5" t="n">
         <v>-14.24</v>
@@ -30302,7 +30308,7 @@
         <v>22</v>
       </c>
       <c r="F1194" s="9" t="n">
-        <v>82.15000000000001</v>
+        <v>82.15</v>
       </c>
       <c r="G1194" s="8" t="n">
         <v>250009</v>
@@ -30327,7 +30333,7 @@
         <v>40</v>
       </c>
       <c r="F1195" s="6" t="n">
-        <v>84.73999999999999</v>
+        <v>84.74</v>
       </c>
       <c r="G1195" s="5" t="n">
         <v>250010</v>
@@ -30377,7 +30383,7 @@
         <v>40</v>
       </c>
       <c r="F1197" s="6" t="n">
-        <v>83.73999999999999</v>
+        <v>83.74</v>
       </c>
       <c r="G1197" s="5" t="n">
         <v>250012</v>
@@ -30452,7 +30458,7 @@
         <v>40</v>
       </c>
       <c r="F1200" s="9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.6</v>
       </c>
       <c r="G1200" s="8" t="n">
         <v>250015</v>
@@ -30477,7 +30483,7 @@
         <v>40</v>
       </c>
       <c r="F1201" s="6" t="n">
-        <v>84.84999999999999</v>
+        <v>84.85</v>
       </c>
       <c r="G1201" s="5" t="n">
         <v>250016</v>
@@ -30527,7 +30533,7 @@
         <v>40</v>
       </c>
       <c r="F1203" s="6" t="n">
-        <v>84.45999999999999</v>
+        <v>84.46</v>
       </c>
       <c r="G1203" s="5" t="n">
         <v>250018</v>
@@ -30577,7 +30583,7 @@
         <v>40</v>
       </c>
       <c r="F1205" s="6" t="n">
-        <v>83.51000000000001</v>
+        <v>83.51</v>
       </c>
       <c r="G1205" s="5" t="n">
         <v>250020</v>
@@ -30702,7 +30708,7 @@
         <v>58</v>
       </c>
       <c r="F1210" s="9" t="n">
-        <v>86.56999999999999</v>
+        <v>86.57</v>
       </c>
       <c r="G1210" s="8" t="n">
         <v>250025</v>
@@ -30777,7 +30783,7 @@
         <v>58</v>
       </c>
       <c r="F1213" s="6" t="n">
-        <v>86.95999999999999</v>
+        <v>86.96</v>
       </c>
       <c r="G1213" s="5" t="n">
         <v>250028</v>
@@ -30852,7 +30858,7 @@
         <v>58</v>
       </c>
       <c r="F1216" s="9" t="n">
-        <v>87.70999999999999</v>
+        <v>87.71</v>
       </c>
       <c r="G1216" s="8" t="n">
         <v>250031</v>
@@ -30918,7 +30924,7 @@
         <v>34</v>
       </c>
       <c r="C1219" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1219" s="5" t="n">
         <v>14.24</v>
@@ -30977,7 +30983,7 @@
         <v>73</v>
       </c>
       <c r="F1221" s="6" t="n">
-        <v>90.73999999999999</v>
+        <v>90.74</v>
       </c>
       <c r="G1221" s="5" t="n">
         <v>250036</v>
@@ -30996,7 +31002,7 @@
         <v>14.24</v>
       </c>
       <c r="D1222" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1222" s="8" t="n">
         <v>73</v>
@@ -31021,7 +31027,7 @@
         <v>-14.24</v>
       </c>
       <c r="D1223" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="E1223" s="5" t="n">
         <v>73</v>
@@ -31077,7 +31083,7 @@
         <v>73</v>
       </c>
       <c r="F1225" s="6" t="n">
-        <v>90.70999999999999</v>
+        <v>90.71</v>
       </c>
       <c r="G1225" s="5" t="n">
         <v>250040</v>
@@ -31093,7 +31099,7 @@
         <v>41</v>
       </c>
       <c r="C1226" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1226" s="8" t="n">
         <v>14.24</v>
@@ -31118,7 +31124,7 @@
         <v>42</v>
       </c>
       <c r="C1227" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="D1227" s="5" t="n">
         <v>-14.24</v>
@@ -31127,7 +31133,7 @@
         <v>73</v>
       </c>
       <c r="F1227" s="6" t="n">
-        <v>90.73999999999999</v>
+        <v>90.74</v>
       </c>
       <c r="G1227" s="5" t="n">
         <v>250042</v>
@@ -31152,7 +31158,7 @@
         <v>73</v>
       </c>
       <c r="F1228" s="9" t="n">
-        <v>90.81999999999999</v>
+        <v>90.82</v>
       </c>
       <c r="G1228" s="8" t="n">
         <v>250043</v>
@@ -31177,7 +31183,7 @@
         <v>73</v>
       </c>
       <c r="F1229" s="6" t="n">
-        <v>90.06999999999999</v>
+        <v>90.07</v>
       </c>
       <c r="G1229" s="5" t="n">
         <v>250044</v>
@@ -31196,13 +31202,13 @@
         <v>-14.24</v>
       </c>
       <c r="D1230" s="8" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1230" s="8" t="n">
         <v>73</v>
       </c>
       <c r="F1230" s="9" t="n">
-        <v>91.45999999999999</v>
+        <v>91.46</v>
       </c>
       <c r="G1230" s="8" t="n">
         <v>250045</v>
@@ -31221,7 +31227,7 @@
         <v>14.24</v>
       </c>
       <c r="D1231" s="5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-71.6</v>
       </c>
       <c r="E1231" s="5" t="n">
         <v>73</v>
@@ -31252,7 +31258,7 @@
         <v>73</v>
       </c>
       <c r="F1232" s="9" t="n">
-        <v>91.51000000000001</v>
+        <v>91.51</v>
       </c>
       <c r="G1232" s="8" t="n">
         <v>250047</v>
@@ -31293,7 +31299,7 @@
         <v>49</v>
       </c>
       <c r="C1234" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.6</v>
       </c>
       <c r="D1234" s="8" t="n">
         <v>-14.24</v>
@@ -31302,7 +31308,7 @@
         <v>73</v>
       </c>
       <c r="F1234" s="9" t="n">
-        <v>90.06999999999999</v>
+        <v>90.07</v>
       </c>
       <c r="G1234" s="8" t="n">
         <v>250049</v>
@@ -31346,6 +31352,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>radius_mm is computed from the site coordinates (=ROUND(SQRT(x^2+y^2),2)).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -31377,13 +31390,14 @@
       <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11">
+        <f>ROUND(SQRT(B5^2+C5^2),2)</f>
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
@@ -31391,19 +31405,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="13">
+        <f>ROUND(SQRT(B6^2+C6^2),2)</f>
         <v>22</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31411,13 +31426,14 @@
       <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>15.56</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>15.56</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11">
+        <f>ROUND(SQRT(B7^2+C7^2),2)</f>
         <v>22</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -31425,19 +31441,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="13">
+        <f>ROUND(SQRT(B8^2+C8^2),2)</f>
         <v>22</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31445,13 +31462,14 @@
       <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>-15.56</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>15.56</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11">
+        <f>ROUND(SQRT(B9^2+C9^2),2)</f>
         <v>22</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -31459,19 +31477,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="13" t="n">
         <v>-22</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="13">
+        <f>ROUND(SQRT(B10^2+C10^2),2)</f>
         <v>22</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31479,13 +31498,14 @@
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>-15.56</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>-15.56</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11">
+        <f>ROUND(SQRT(B11^2+C11^2),2)</f>
         <v>22</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -31493,19 +31513,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
         <v>-0</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="13" t="n">
         <v>-22</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="13">
+        <f>ROUND(SQRT(B12^2+C12^2),2)</f>
         <v>22</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31513,13 +31534,14 @@
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>15.56</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <v>-15.56</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11">
+        <f>ROUND(SQRT(B13^2+C13^2),2)</f>
         <v>22</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -31527,19 +31549,20 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="13" t="n">
         <v>38.64</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="13" t="n">
         <v>10.35</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="D14" s="13">
+        <f>ROUND(SQRT(B14^2+C14^2),2)</f>
+        <v>40</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31547,13 +31570,14 @@
       <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>28.28</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="11" t="n">
         <v>28.28</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11">
+        <f>ROUND(SQRT(B15^2+C15^2),2)</f>
         <v>40</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -31561,19 +31585,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="13" t="n">
         <v>10.35</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="13" t="n">
         <v>38.64</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" s="11" t="n">
+      <c r="D16" s="13">
+        <f>ROUND(SQRT(B16^2+C16^2),2)</f>
+        <v>40</v>
+      </c>
+      <c r="E16" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31581,13 +31606,14 @@
       <c r="A17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="11" t="n">
         <v>-10.35</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="11" t="n">
         <v>38.64</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11">
+        <f>ROUND(SQRT(B17^2+C17^2),2)</f>
         <v>40</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -31595,19 +31621,20 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="13" t="n">
         <v>-28.28</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="13" t="n">
         <v>28.28</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="D18" s="13">
+        <f>ROUND(SQRT(B18^2+C18^2),2)</f>
+        <v>40</v>
+      </c>
+      <c r="E18" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31615,13 +31642,14 @@
       <c r="A19" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <v>-38.64</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="11" t="n">
         <v>10.35</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11">
+        <f>ROUND(SQRT(B19^2+C19^2),2)</f>
         <v>40</v>
       </c>
       <c r="E19" s="10" t="n">
@@ -31629,19 +31657,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="13" t="n">
         <v>-38.64</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="13" t="n">
         <v>-10.35</v>
       </c>
-      <c r="D20" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" s="11" t="n">
+      <c r="D20" s="13">
+        <f>ROUND(SQRT(B20^2+C20^2),2)</f>
+        <v>40</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31649,13 +31678,14 @@
       <c r="A21" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="11" t="n">
         <v>-28.28</v>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="11" t="n">
         <v>-28.28</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="11">
+        <f>ROUND(SQRT(B21^2+C21^2),2)</f>
         <v>40</v>
       </c>
       <c r="E21" s="10" t="n">
@@ -31663,19 +31693,20 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="13" t="n">
         <v>-10.35</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="13" t="n">
         <v>-38.64</v>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E22" s="11" t="n">
+      <c r="D22" s="13">
+        <f>ROUND(SQRT(B22^2+C22^2),2)</f>
+        <v>40</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31683,13 +31714,14 @@
       <c r="A23" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="11" t="n">
         <v>10.35</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="11" t="n">
         <v>-38.64</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="11">
+        <f>ROUND(SQRT(B23^2+C23^2),2)</f>
         <v>40</v>
       </c>
       <c r="E23" s="10" t="n">
@@ -31697,19 +31729,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="13" t="n">
         <v>28.28</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="13" t="n">
         <v>-28.28</v>
       </c>
-      <c r="D24" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E24" s="11" t="n">
+      <c r="D24" s="13">
+        <f>ROUND(SQRT(B24^2+C24^2),2)</f>
+        <v>40</v>
+      </c>
+      <c r="E24" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31717,13 +31750,14 @@
       <c r="A25" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="11" t="n">
         <v>38.64</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="11" t="n">
         <v>-10.35</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11">
+        <f>ROUND(SQRT(B25^2+C25^2),2)</f>
         <v>40</v>
       </c>
       <c r="E25" s="10" t="n">
@@ -31731,19 +31765,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="C26" s="11" t="n">
+      <c r="B26" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="C26" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E26" s="11" t="n">
+      <c r="D26" s="13">
+        <f>ROUND(SQRT(B26^2+C26^2),2)</f>
+        <v>58</v>
+      </c>
+      <c r="E26" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31751,13 +31786,14 @@
       <c r="A27" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="11" t="n">
         <v>50.23</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="11">
+        <f>ROUND(SQRT(B27^2+C27^2),2)</f>
         <v>58</v>
       </c>
       <c r="E27" s="10" t="n">
@@ -31765,19 +31801,20 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="13" t="n">
         <v>50.23</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E28" s="11" t="n">
+      <c r="D28" s="13">
+        <f>ROUND(SQRT(B28^2+C28^2),2)</f>
+        <v>58</v>
+      </c>
+      <c r="E28" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31785,13 +31822,14 @@
       <c r="A29" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="D29" s="10" t="n">
+      <c r="C29" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="D29" s="11">
+        <f>ROUND(SQRT(B29^2+C29^2),2)</f>
         <v>58</v>
       </c>
       <c r="E29" s="10" t="n">
@@ -31799,19 +31837,20 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="13" t="n">
         <v>-29</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="13" t="n">
         <v>50.23</v>
       </c>
-      <c r="D30" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E30" s="11" t="n">
+      <c r="D30" s="13">
+        <f>ROUND(SQRT(B30^2+C30^2),2)</f>
+        <v>58</v>
+      </c>
+      <c r="E30" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31819,13 +31858,14 @@
       <c r="A31" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" s="11" t="n">
         <v>-50.23</v>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="11">
+        <f>ROUND(SQRT(B31^2+C31^2),2)</f>
         <v>58</v>
       </c>
       <c r="E31" s="10" t="n">
@@ -31833,19 +31873,20 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="13" t="n">
         <v>-58</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E32" s="11" t="n">
+      <c r="D32" s="13">
+        <f>ROUND(SQRT(B32^2+C32^2),2)</f>
+        <v>58</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31853,13 +31894,14 @@
       <c r="A33" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="10" t="n">
+      <c r="B33" s="11" t="n">
         <v>-50.23</v>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="11">
+        <f>ROUND(SQRT(B33^2+C33^2),2)</f>
         <v>58</v>
       </c>
       <c r="E33" s="10" t="n">
@@ -31867,19 +31909,20 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="13" t="n">
         <v>-29</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C34" s="13" t="n">
         <v>-50.23</v>
       </c>
-      <c r="D34" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" s="11" t="n">
+      <c r="D34" s="13">
+        <f>ROUND(SQRT(B34^2+C34^2),2)</f>
+        <v>58</v>
+      </c>
+      <c r="E34" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31887,13 +31930,14 @@
       <c r="A35" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="10" t="n">
+      <c r="B35" s="11" t="n">
         <v>-0</v>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D35" s="11">
+        <f>ROUND(SQRT(B35^2+C35^2),2)</f>
         <v>58</v>
       </c>
       <c r="E35" s="10" t="n">
@@ -31901,19 +31945,20 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="n">
+      <c r="B36" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C36" s="13" t="n">
         <v>-50.23</v>
       </c>
-      <c r="D36" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" s="11" t="n">
+      <c r="D36" s="13">
+        <f>ROUND(SQRT(B36^2+C36^2),2)</f>
+        <v>58</v>
+      </c>
+      <c r="E36" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31921,13 +31966,14 @@
       <c r="A37" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B37" s="11" t="n">
         <v>50.23</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="11">
+        <f>ROUND(SQRT(B37^2+C37^2),2)</f>
         <v>58</v>
       </c>
       <c r="E37" s="10" t="n">
@@ -31935,19 +31981,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="11" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="C38" s="11" t="n">
+      <c r="B38" s="13" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="C38" s="13" t="n">
         <v>14.24</v>
       </c>
-      <c r="D38" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E38" s="11" t="n">
+      <c r="D38" s="13">
+        <f>ROUND(SQRT(B38^2+C38^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E38" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31955,13 +32002,14 @@
       <c r="A39" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="n">
+      <c r="B39" s="11" t="n">
         <v>60.7</v>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="11" t="n">
         <v>40.56</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="11">
+        <f>ROUND(SQRT(B39^2+C39^2),2)</f>
         <v>73</v>
       </c>
       <c r="E39" s="10" t="n">
@@ -31969,19 +32017,20 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="13" t="n">
         <v>40.56</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="13" t="n">
         <v>60.7</v>
       </c>
-      <c r="D40" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E40" s="11" t="n">
+      <c r="D40" s="13">
+        <f>ROUND(SQRT(B40^2+C40^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E40" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31989,13 +32038,14 @@
       <c r="A41" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="10" t="n">
+      <c r="B41" s="11" t="n">
         <v>14.24</v>
       </c>
-      <c r="C41" s="10" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="D41" s="10" t="n">
+      <c r="C41" s="11" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="D41" s="11">
+        <f>ROUND(SQRT(B41^2+C41^2),2)</f>
         <v>73</v>
       </c>
       <c r="E41" s="10" t="n">
@@ -32003,19 +32053,20 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
+      <c r="A42" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="11" t="n">
+      <c r="B42" s="13" t="n">
         <v>-14.24</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E42" s="11" t="n">
+      <c r="C42" s="13" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="D42" s="13">
+        <f>ROUND(SQRT(B42^2+C42^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E42" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32023,13 +32074,14 @@
       <c r="A43" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="n">
+      <c r="B43" s="11" t="n">
         <v>-40.56</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="11" t="n">
         <v>60.7</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="11">
+        <f>ROUND(SQRT(B43^2+C43^2),2)</f>
         <v>73</v>
       </c>
       <c r="E43" s="10" t="n">
@@ -32037,19 +32089,20 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="11" t="n">
+      <c r="A44" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="13" t="n">
         <v>-60.7</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C44" s="13" t="n">
         <v>40.56</v>
       </c>
-      <c r="D44" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E44" s="11" t="n">
+      <c r="D44" s="13">
+        <f>ROUND(SQRT(B44^2+C44^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E44" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32057,13 +32110,14 @@
       <c r="A45" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="n">
-        <v>-71.59999999999999</v>
-      </c>
-      <c r="C45" s="10" t="n">
+      <c r="B45" s="11" t="n">
+        <v>-71.6</v>
+      </c>
+      <c r="C45" s="11" t="n">
         <v>14.24</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="11">
+        <f>ROUND(SQRT(B45^2+C45^2),2)</f>
         <v>73</v>
       </c>
       <c r="E45" s="10" t="n">
@@ -32071,19 +32125,20 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
+      <c r="A46" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="11" t="n">
-        <v>-71.59999999999999</v>
-      </c>
-      <c r="C46" s="11" t="n">
+      <c r="B46" s="13" t="n">
+        <v>-71.6</v>
+      </c>
+      <c r="C46" s="13" t="n">
         <v>-14.24</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E46" s="11" t="n">
+      <c r="D46" s="13">
+        <f>ROUND(SQRT(B46^2+C46^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32091,13 +32146,14 @@
       <c r="A47" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="n">
+      <c r="B47" s="11" t="n">
         <v>-60.7</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="11" t="n">
         <v>-40.56</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="11">
+        <f>ROUND(SQRT(B47^2+C47^2),2)</f>
         <v>73</v>
       </c>
       <c r="E47" s="10" t="n">
@@ -32105,19 +32161,20 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B48" s="13" t="n">
         <v>-40.56</v>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="13" t="n">
         <v>-60.7</v>
       </c>
-      <c r="D48" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E48" s="11" t="n">
+      <c r="D48" s="13">
+        <f>ROUND(SQRT(B48^2+C48^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E48" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32125,13 +32182,14 @@
       <c r="A49" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="n">
+      <c r="B49" s="11" t="n">
         <v>-14.24</v>
       </c>
-      <c r="C49" s="10" t="n">
-        <v>-71.59999999999999</v>
-      </c>
-      <c r="D49" s="10" t="n">
+      <c r="C49" s="11" t="n">
+        <v>-71.6</v>
+      </c>
+      <c r="D49" s="11">
+        <f>ROUND(SQRT(B49^2+C49^2),2)</f>
         <v>73</v>
       </c>
       <c r="E49" s="10" t="n">
@@ -32139,19 +32197,20 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="n">
+      <c r="A50" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="B50" s="13" t="n">
         <v>14.24</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>-71.59999999999999</v>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E50" s="11" t="n">
+      <c r="C50" s="13" t="n">
+        <v>-71.6</v>
+      </c>
+      <c r="D50" s="13">
+        <f>ROUND(SQRT(B50^2+C50^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32159,13 +32218,14 @@
       <c r="A51" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="10" t="n">
+      <c r="B51" s="11" t="n">
         <v>40.56</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="11" t="n">
         <v>-60.7</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="11">
+        <f>ROUND(SQRT(B51^2+C51^2),2)</f>
         <v>73</v>
       </c>
       <c r="E51" s="10" t="n">
@@ -32173,19 +32233,20 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="n">
+      <c r="B52" s="13" t="n">
         <v>60.7</v>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="13" t="n">
         <v>-40.56</v>
       </c>
-      <c r="D52" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E52" s="11" t="n">
+      <c r="D52" s="13">
+        <f>ROUND(SQRT(B52^2+C52^2),2)</f>
+        <v>73</v>
+      </c>
+      <c r="E52" s="12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32193,13 +32254,14 @@
       <c r="A53" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="C53" s="10" t="n">
+      <c r="B53" s="11" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="C53" s="11" t="n">
         <v>-14.24</v>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D53" s="11">
+        <f>ROUND(SQRT(B53^2+C53^2),2)</f>
         <v>73</v>
       </c>
       <c r="E53" s="10" t="n">
@@ -32207,8 +32269,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
